--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_recreation.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_recreation.xlsx
@@ -1127,43 +1127,43 @@
         <v>15.4054054054054</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>71.4352255870117</v>
       </c>
       <c r="G2">
         <v>1.55339805825243</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.231019417475728</v>
       </c>
       <c r="I2">
         <v>0.0672410170203824</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>443.9</v>
       </c>
       <c r="L2">
-        <v>485.761742892382</v>
+        <v>480.565983094794</v>
       </c>
       <c r="M2">
         <v>437.2</v>
       </c>
       <c r="N2">
-        <v>447.061742892382</v>
+        <v>446.624983094794</v>
       </c>
       <c r="O2">
         <v>32</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>4.759</v>
       </c>
       <c r="Q2">
         <v>0.09285439827844889</v>
       </c>
       <c r="R2">
-        <v>0.0918164244747063</v>
+        <v>0.0918614244747063</v>
       </c>
       <c r="S2">
         <v>0.0612366166625341</v>
@@ -1185,13 +1185,13 @@
         <v>0.0951336706634664</v>
       </c>
       <c r="X2">
-        <v>0.0918164244747063</v>
+        <v>0.0922812368431377</v>
       </c>
       <c r="Y2">
         <v>0.961605065943878</v>
       </c>
       <c r="Z2">
-        <v>0.896945763337859</v>
+        <v>0.906005821553393</v>
       </c>
       <c r="AA2">
         <v>32</v>
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09181642447470628</v>
+        <v>0.09186142447470629</v>
       </c>
       <c r="C2">
-        <v>485.7617428923816</v>
+        <v>480.5659830947942</v>
       </c>
       <c r="D2">
-        <v>447.0617428923816</v>
+        <v>446.6249830947942</v>
       </c>
       <c r="E2">
-        <v>-32</v>
+        <v>-27.241</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.758999999999999</v>
       </c>
       <c r="G2">
         <v>38.7</v>
@@ -1445,28 +1445,28 @@
         <v>17.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2393777</v>
       </c>
       <c r="N2">
-        <v>17.1</v>
+        <v>16.8606223</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>17.1</v>
+        <v>16.8606223</v>
       </c>
       <c r="Q2">
-        <v>20.6</v>
+        <v>20.3606223</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09181642447470628</v>
+        <v>0.09228123684313766</v>
       </c>
       <c r="T2">
-        <v>0.8969457633378592</v>
+        <v>0.9060058215533933</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>71.43522558701167</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09186142447470629</v>
+        <v>0.09190642447470629</v>
       </c>
       <c r="C3">
-        <v>480.5659830947942</v>
+        <v>475.3710758547893</v>
       </c>
       <c r="D3">
-        <v>446.6249830947942</v>
+        <v>446.1890758547893</v>
       </c>
       <c r="E3">
-        <v>-27.241</v>
+        <v>-22.482</v>
       </c>
       <c r="F3">
-        <v>4.758999999999999</v>
+        <v>9.517999999999999</v>
       </c>
       <c r="G3">
         <v>38.7</v>
@@ -1527,28 +1527,28 @@
         <v>17.1</v>
       </c>
       <c r="M3">
-        <v>0.2393777</v>
+        <v>0.4787553999999999</v>
       </c>
       <c r="N3">
-        <v>16.8606223</v>
+        <v>16.6212446</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>16.8606223</v>
+        <v>16.6212446</v>
       </c>
       <c r="Q3">
-        <v>20.3606223</v>
+        <v>20.1212446</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09228123684313766</v>
+        <v>0.09275553517827172</v>
       </c>
       <c r="T3">
-        <v>0.9060058215533933</v>
+        <v>0.9152507789161829</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>71.43522558701167</v>
+        <v>35.71761279350584</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09190642447470629</v>
+        <v>0.09195142447470626</v>
       </c>
       <c r="C4">
-        <v>475.3710758547893</v>
+        <v>470.1770186785052</v>
       </c>
       <c r="D4">
-        <v>446.1890758547893</v>
+        <v>445.7540186785052</v>
       </c>
       <c r="E4">
-        <v>-22.482</v>
+        <v>-17.723</v>
       </c>
       <c r="F4">
-        <v>9.517999999999999</v>
+        <v>14.277</v>
       </c>
       <c r="G4">
         <v>38.7</v>
@@ -1609,28 +1609,28 @@
         <v>17.1</v>
       </c>
       <c r="M4">
-        <v>0.4787553999999999</v>
+        <v>0.7181331</v>
       </c>
       <c r="N4">
-        <v>16.6212446</v>
+        <v>16.3818669</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>16.6212446</v>
+        <v>16.3818669</v>
       </c>
       <c r="Q4">
-        <v>20.1212446</v>
+        <v>19.8818669</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09275553517827172</v>
+        <v>0.09323961286052193</v>
       </c>
       <c r="T4">
-        <v>0.9152507789161829</v>
+        <v>0.9246863539565559</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>35.71761279350584</v>
+        <v>23.81174186233722</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09195142447470626</v>
+        <v>0.0919964244747063</v>
       </c>
       <c r="C5">
-        <v>470.1770186785052</v>
+        <v>464.9838090817964</v>
       </c>
       <c r="D5">
-        <v>445.7540186785052</v>
+        <v>445.3198090817964</v>
       </c>
       <c r="E5">
-        <v>-17.723</v>
+        <v>-12.964</v>
       </c>
       <c r="F5">
-        <v>14.277</v>
+        <v>19.036</v>
       </c>
       <c r="G5">
         <v>38.7</v>
@@ -1691,28 +1691,28 @@
         <v>17.1</v>
       </c>
       <c r="M5">
-        <v>0.7181331</v>
+        <v>0.9575107999999999</v>
       </c>
       <c r="N5">
-        <v>16.3818669</v>
+        <v>16.1424892</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>16.3818669</v>
+        <v>16.1424892</v>
       </c>
       <c r="Q5">
-        <v>19.8818669</v>
+        <v>19.6424892</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09323961286052193</v>
+        <v>0.09373377549448572</v>
       </c>
       <c r="T5">
-        <v>0.9246863539565559</v>
+        <v>0.9343185034769368</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>23.81174186233722</v>
+        <v>17.85880639675291</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0919964244747063</v>
+        <v>0.09204142447470628</v>
       </c>
       <c r="C6">
-        <v>464.9838090817964</v>
+        <v>459.7914445901891</v>
       </c>
       <c r="D6">
-        <v>445.3198090817964</v>
+        <v>444.8864445901892</v>
       </c>
       <c r="E6">
-        <v>-12.964</v>
+        <v>-8.204999999999995</v>
       </c>
       <c r="F6">
-        <v>19.036</v>
+        <v>23.795</v>
       </c>
       <c r="G6">
         <v>38.7</v>
@@ -1773,28 +1773,28 @@
         <v>17.1</v>
       </c>
       <c r="M6">
-        <v>0.9575107999999999</v>
+        <v>1.1968885</v>
       </c>
       <c r="N6">
-        <v>16.1424892</v>
+        <v>15.9031115</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>16.1424892</v>
+        <v>15.9031115</v>
       </c>
       <c r="Q6">
-        <v>19.6424892</v>
+        <v>19.4031115</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09373377549448572</v>
+        <v>0.0942383415523224</v>
       </c>
       <c r="T6">
-        <v>0.9343185034769368</v>
+        <v>0.9441534350924834</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>17.85880639675291</v>
+        <v>14.28704511740233</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09204142447470628</v>
+        <v>0.09217642447470627</v>
       </c>
       <c r="C7">
-        <v>459.7914445901891</v>
+        <v>453.7373971452871</v>
       </c>
       <c r="D7">
-        <v>444.8864445901892</v>
+        <v>443.5913971452871</v>
       </c>
       <c r="E7">
-        <v>-8.204999999999995</v>
+        <v>-3.445999999999994</v>
       </c>
       <c r="F7">
-        <v>23.795</v>
+        <v>28.554</v>
       </c>
       <c r="G7">
         <v>38.7</v>
@@ -1855,45 +1855,45 @@
         <v>17.1</v>
       </c>
       <c r="M7">
-        <v>1.1968885</v>
+        <v>1.4790972</v>
       </c>
       <c r="N7">
-        <v>15.9031115</v>
+        <v>15.6209028</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>15.9031115</v>
+        <v>15.6209028</v>
       </c>
       <c r="Q7">
-        <v>19.4031115</v>
+        <v>19.1209028</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0942383415523224</v>
+        <v>0.09475364305819817</v>
       </c>
       <c r="T7">
-        <v>0.9441534350924834</v>
+        <v>0.9541976205721907</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0</v>
       </c>
       <c r="W7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>14.28704511740233</v>
+        <v>11.56110632891469</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09217642447470627</v>
+        <v>0.0922364244747063</v>
       </c>
       <c r="C8">
-        <v>453.7373971452871</v>
+        <v>448.4052375161853</v>
       </c>
       <c r="D8">
-        <v>443.5913971452871</v>
+        <v>443.0182375161853</v>
       </c>
       <c r="E8">
-        <v>-3.445999999999998</v>
+        <v>1.312999999999999</v>
       </c>
       <c r="F8">
-        <v>28.554</v>
+        <v>33.313</v>
       </c>
       <c r="G8">
         <v>38.7</v>
@@ -1937,28 +1937,28 @@
         <v>17.1</v>
       </c>
       <c r="M8">
-        <v>1.4790972</v>
+        <v>1.7256134</v>
       </c>
       <c r="N8">
-        <v>15.6209028</v>
+        <v>15.3743866</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>15.6209028</v>
+        <v>15.3743866</v>
       </c>
       <c r="Q8">
-        <v>19.1209028</v>
+        <v>18.8743866</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09475364305819817</v>
+        <v>0.09528002631688848</v>
       </c>
       <c r="T8">
-        <v>0.9541976205721907</v>
+        <v>0.9644578100407089</v>
       </c>
       <c r="U8">
         <v>0.0518</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>11.5611063289147</v>
+        <v>9.90951971049831</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09223642447470629</v>
+        <v>0.09243242447470627</v>
       </c>
       <c r="C9">
-        <v>448.4052375161855</v>
+        <v>441.7841946236855</v>
       </c>
       <c r="D9">
-        <v>443.0182375161855</v>
+        <v>441.1561946236855</v>
       </c>
       <c r="E9">
-        <v>1.313000000000006</v>
+        <v>6.071999999999999</v>
       </c>
       <c r="F9">
-        <v>33.313</v>
+        <v>38.072</v>
       </c>
       <c r="G9">
         <v>38.7</v>
@@ -2019,45 +2019,45 @@
         <v>17.1</v>
       </c>
       <c r="M9">
-        <v>1.7256134</v>
+        <v>2.036852</v>
       </c>
       <c r="N9">
-        <v>15.3743866</v>
+        <v>15.063148</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>15.3743866</v>
+        <v>15.063148</v>
       </c>
       <c r="Q9">
-        <v>18.8743866</v>
+        <v>18.563148</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09528002631688848</v>
+        <v>0.09581785268989812</v>
       </c>
       <c r="T9">
-        <v>0.9644578100407089</v>
+        <v>0.9749410471063686</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0</v>
       </c>
       <c r="W9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>9.909519710498307</v>
+        <v>8.395308053800671</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09243242447470627</v>
+        <v>0.0925814244747063</v>
       </c>
       <c r="C10">
-        <v>441.7841946236855</v>
+        <v>435.6201011760826</v>
       </c>
       <c r="D10">
-        <v>441.1561946236855</v>
+        <v>439.7511011760827</v>
       </c>
       <c r="E10">
-        <v>6.071999999999999</v>
+        <v>10.831</v>
       </c>
       <c r="F10">
-        <v>38.072</v>
+        <v>42.831</v>
       </c>
       <c r="G10">
         <v>38.7</v>
@@ -2101,45 +2101,45 @@
         <v>17.1</v>
       </c>
       <c r="M10">
-        <v>2.036852</v>
+        <v>2.3257233</v>
       </c>
       <c r="N10">
-        <v>15.063148</v>
+        <v>14.7742767</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>15.063148</v>
+        <v>14.7742767</v>
       </c>
       <c r="Q10">
-        <v>18.563148</v>
+        <v>18.2742767</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09581785268989812</v>
+        <v>0.09636749942275416</v>
       </c>
       <c r="T10">
-        <v>0.9749410471063686</v>
+        <v>0.9856546849866586</v>
       </c>
       <c r="U10">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V10">
         <v>0</v>
       </c>
       <c r="W10">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y10">
-        <v>8.395308053800671</v>
+        <v>7.35255135466889</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0925814244747063</v>
+        <v>0.0926664244747063</v>
       </c>
       <c r="C11">
-        <v>435.6201011760826</v>
+        <v>430.0635399364762</v>
       </c>
       <c r="D11">
-        <v>439.7511011760827</v>
+        <v>438.9535399364762</v>
       </c>
       <c r="E11">
-        <v>10.831</v>
+        <v>15.59</v>
       </c>
       <c r="F11">
-        <v>42.831</v>
+        <v>47.59</v>
       </c>
       <c r="G11">
         <v>38.7</v>
@@ -2183,28 +2183,28 @@
         <v>17.1</v>
       </c>
       <c r="M11">
-        <v>2.3257233</v>
+        <v>2.584137</v>
       </c>
       <c r="N11">
-        <v>14.7742767</v>
+        <v>14.515863</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>14.7742767</v>
+        <v>14.515863</v>
       </c>
       <c r="Q11">
-        <v>18.2742767</v>
+        <v>18.015863</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09636749942275416</v>
+        <v>0.09692936052745144</v>
       </c>
       <c r="T11">
-        <v>0.9856546849866586</v>
+        <v>0.9966064037087325</v>
       </c>
       <c r="U11">
         <v>0.0543</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>7.35255135466889</v>
+        <v>6.617296219202002</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0926664244747063</v>
+        <v>0.09286142447470629</v>
       </c>
       <c r="C12">
-        <v>430.0635399364762</v>
+        <v>423.4857267313296</v>
       </c>
       <c r="D12">
-        <v>438.9535399364762</v>
+        <v>437.1347267313296</v>
       </c>
       <c r="E12">
-        <v>15.59000000000001</v>
+        <v>20.349</v>
       </c>
       <c r="F12">
-        <v>47.59</v>
+        <v>52.349</v>
       </c>
       <c r="G12">
         <v>38.7</v>
@@ -2265,45 +2265,45 @@
         <v>17.1</v>
       </c>
       <c r="M12">
-        <v>2.584137</v>
+        <v>2.8948997</v>
       </c>
       <c r="N12">
-        <v>14.515863</v>
+        <v>14.2051003</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>14.515863</v>
+        <v>14.2051003</v>
       </c>
       <c r="Q12">
-        <v>18.015863</v>
+        <v>17.7051003</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09692936052745144</v>
+        <v>0.09750384772438908</v>
       </c>
       <c r="T12">
-        <v>0.9966064037087325</v>
+        <v>1.007804228469505</v>
       </c>
       <c r="U12">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V12">
         <v>0</v>
       </c>
       <c r="W12">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y12">
-        <v>6.617296219202001</v>
+        <v>5.906940402805666</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09286142447470629</v>
+        <v>0.09295642447470627</v>
       </c>
       <c r="C13">
-        <v>423.4857267313296</v>
+        <v>417.8460874652685</v>
       </c>
       <c r="D13">
-        <v>437.1347267313296</v>
+        <v>436.2540874652685</v>
       </c>
       <c r="E13">
-        <v>20.349</v>
+        <v>25.108</v>
       </c>
       <c r="F13">
-        <v>52.349</v>
+        <v>57.108</v>
       </c>
       <c r="G13">
         <v>38.7</v>
@@ -2347,28 +2347,28 @@
         <v>17.1</v>
       </c>
       <c r="M13">
-        <v>2.8948997</v>
+        <v>3.1580724</v>
       </c>
       <c r="N13">
-        <v>14.2051003</v>
+        <v>13.9419276</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>14.2051003</v>
+        <v>13.9419276</v>
       </c>
       <c r="Q13">
-        <v>17.7051003</v>
+        <v>17.4419276</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09750384772438908</v>
+        <v>0.09809139144852985</v>
       </c>
       <c r="T13">
-        <v>1.007804228469505</v>
+        <v>1.019256549247567</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.906940402805666</v>
+        <v>5.414695369238527</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09295642447470627</v>
+        <v>0.09305142447470628</v>
       </c>
       <c r="C14">
-        <v>417.8460874652685</v>
+        <v>412.2099892873841</v>
       </c>
       <c r="D14">
-        <v>436.2540874652685</v>
+        <v>435.3769892873841</v>
       </c>
       <c r="E14">
-        <v>25.108</v>
+        <v>29.867</v>
       </c>
       <c r="F14">
-        <v>57.108</v>
+        <v>61.867</v>
       </c>
       <c r="G14">
         <v>38.7</v>
@@ -2429,28 +2429,28 @@
         <v>17.1</v>
       </c>
       <c r="M14">
-        <v>3.1580724</v>
+        <v>3.4212451</v>
       </c>
       <c r="N14">
-        <v>13.9419276</v>
+        <v>13.6787549</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>13.9419276</v>
+        <v>13.6787549</v>
       </c>
       <c r="Q14">
-        <v>17.4419276</v>
+        <v>17.1787549</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09809139144852985</v>
+        <v>0.09869244192494975</v>
       </c>
       <c r="T14">
-        <v>1.019256549247567</v>
+        <v>1.030972141767654</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.414695369238527</v>
+        <v>4.998180340835564</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09305142447470628</v>
+        <v>0.09314642447470628</v>
       </c>
       <c r="C15">
-        <v>412.2099892873841</v>
+        <v>406.5774108822313</v>
       </c>
       <c r="D15">
-        <v>435.3769892873841</v>
+        <v>434.5034108822314</v>
       </c>
       <c r="E15">
-        <v>29.867</v>
+        <v>34.626</v>
       </c>
       <c r="F15">
-        <v>61.867</v>
+        <v>66.626</v>
       </c>
       <c r="G15">
         <v>38.7</v>
@@ -2511,28 +2511,28 @@
         <v>17.1</v>
       </c>
       <c r="M15">
-        <v>3.4212451</v>
+        <v>3.6844178</v>
       </c>
       <c r="N15">
-        <v>13.6787549</v>
+        <v>13.4155822</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>13.6787549</v>
+        <v>13.4155822</v>
       </c>
       <c r="Q15">
-        <v>17.1787549</v>
+        <v>16.9155822</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09869244192494975</v>
+        <v>0.09930747031942591</v>
       </c>
       <c r="T15">
-        <v>1.030972141767654</v>
+        <v>1.042960189927743</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>4.998180340835564</v>
+        <v>4.641167459347308</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09314642447470628</v>
+        <v>0.09361642447470628</v>
       </c>
       <c r="C16">
-        <v>406.5774108822313</v>
+        <v>397.5475645076206</v>
       </c>
       <c r="D16">
-        <v>434.5034108822314</v>
+        <v>430.2325645076206</v>
       </c>
       <c r="E16">
-        <v>34.626</v>
+        <v>39.38500000000001</v>
       </c>
       <c r="F16">
-        <v>66.626</v>
+        <v>71.38500000000001</v>
       </c>
       <c r="G16">
         <v>38.7</v>
@@ -2593,45 +2593,45 @@
         <v>17.1</v>
       </c>
       <c r="M16">
-        <v>3.6844178</v>
+        <v>4.126053000000001</v>
       </c>
       <c r="N16">
-        <v>13.4155822</v>
+        <v>12.973947</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>13.4155822</v>
+        <v>12.973947</v>
       </c>
       <c r="Q16">
-        <v>16.9155822</v>
+        <v>16.473947</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09930747031942591</v>
+        <v>0.09993696997024268</v>
       </c>
       <c r="T16">
-        <v>1.042960189927743</v>
+        <v>1.055230309809246</v>
       </c>
       <c r="U16">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V16">
         <v>0</v>
       </c>
       <c r="W16">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.641167459347308</v>
+        <v>4.144396594033086</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09361642447470628</v>
+        <v>0.09429642447470626</v>
       </c>
       <c r="C17">
-        <v>397.5475645076206</v>
+        <v>386.7559930957269</v>
       </c>
       <c r="D17">
-        <v>430.2325645076206</v>
+        <v>424.1999930957269</v>
       </c>
       <c r="E17">
-        <v>39.38499999999999</v>
+        <v>44.14399999999999</v>
       </c>
       <c r="F17">
-        <v>71.38499999999999</v>
+        <v>76.14399999999999</v>
       </c>
       <c r="G17">
         <v>38.7</v>
@@ -2675,45 +2675,45 @@
         <v>17.1</v>
       </c>
       <c r="M17">
-        <v>4.126053</v>
+        <v>4.667627199999999</v>
       </c>
       <c r="N17">
-        <v>12.973947</v>
+        <v>12.4323728</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>12.973947</v>
+        <v>12.4323728</v>
       </c>
       <c r="Q17">
-        <v>16.473947</v>
+        <v>15.9323728</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09993696997024268</v>
+        <v>0.1005814577079837</v>
       </c>
       <c r="T17">
-        <v>1.055230309809246</v>
+        <v>1.067792575402213</v>
       </c>
       <c r="U17">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V17">
         <v>0</v>
       </c>
       <c r="W17">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.144396594033088</v>
+        <v>3.663531654798825</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09429642447470626</v>
+        <v>0.09492742447470628</v>
       </c>
       <c r="C18">
-        <v>386.7559930957269</v>
+        <v>376.5485048326952</v>
       </c>
       <c r="D18">
-        <v>424.1999930957269</v>
+        <v>418.7515048326952</v>
       </c>
       <c r="E18">
-        <v>44.14399999999999</v>
+        <v>48.90300000000001</v>
       </c>
       <c r="F18">
-        <v>76.14399999999999</v>
+        <v>80.90300000000001</v>
       </c>
       <c r="G18">
         <v>38.7</v>
@@ -2757,45 +2757,45 @@
         <v>17.1</v>
       </c>
       <c r="M18">
-        <v>4.667627199999999</v>
+        <v>5.1858823</v>
       </c>
       <c r="N18">
-        <v>12.4323728</v>
+        <v>11.9141177</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>12.4323728</v>
+        <v>11.9141177</v>
       </c>
       <c r="Q18">
-        <v>15.9323728</v>
+        <v>15.4141177</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1005814577079837</v>
+        <v>0.1012414752707305</v>
       </c>
       <c r="T18">
-        <v>1.067792575402213</v>
+        <v>1.080657546190192</v>
       </c>
       <c r="U18">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V18">
         <v>0</v>
       </c>
       <c r="W18">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>3.663531654798825</v>
+        <v>3.297413826765795</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09492742447470628</v>
+        <v>0.09511042447470629</v>
       </c>
       <c r="C19">
-        <v>376.5485048326952</v>
+        <v>370.2354414434479</v>
       </c>
       <c r="D19">
-        <v>418.7515048326952</v>
+        <v>417.1974414434479</v>
       </c>
       <c r="E19">
-        <v>48.90300000000001</v>
+        <v>53.66200000000001</v>
       </c>
       <c r="F19">
-        <v>80.90300000000001</v>
+        <v>85.66200000000001</v>
       </c>
       <c r="G19">
         <v>38.7</v>
@@ -2839,28 +2839,28 @@
         <v>17.1</v>
       </c>
       <c r="M19">
-        <v>5.1858823</v>
+        <v>5.490934200000001</v>
       </c>
       <c r="N19">
-        <v>11.9141177</v>
+        <v>11.6090658</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>11.9141177</v>
+        <v>11.6090658</v>
       </c>
       <c r="Q19">
-        <v>15.4141177</v>
+        <v>15.1090658</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1012414752707305</v>
+        <v>0.1019175908228125</v>
       </c>
       <c r="T19">
-        <v>1.080657546190192</v>
+        <v>1.093836296753487</v>
       </c>
       <c r="U19">
         <v>0.0641</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.297413826765795</v>
+        <v>3.11422416972325</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0951104244747063</v>
+        <v>0.09677542447470629</v>
       </c>
       <c r="C20">
-        <v>370.2354414434478</v>
+        <v>351.8496056267493</v>
       </c>
       <c r="D20">
-        <v>417.1974414434478</v>
+        <v>403.5706056267493</v>
       </c>
       <c r="E20">
-        <v>53.66199999999999</v>
+        <v>58.42099999999999</v>
       </c>
       <c r="F20">
-        <v>85.66199999999999</v>
+        <v>90.42099999999999</v>
       </c>
       <c r="G20">
         <v>38.7</v>
@@ -2921,45 +2921,45 @@
         <v>17.1</v>
       </c>
       <c r="M20">
-        <v>5.4909342</v>
+        <v>6.5012699</v>
       </c>
       <c r="N20">
-        <v>11.6090658</v>
+        <v>10.5987301</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>11.6090658</v>
+        <v>10.5987301</v>
       </c>
       <c r="Q20">
-        <v>15.1090658</v>
+        <v>14.0987301</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1019175908228125</v>
+        <v>0.1026104005860571</v>
       </c>
       <c r="T20">
-        <v>1.093836296753487</v>
+        <v>1.107340448565258</v>
       </c>
       <c r="U20">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V20">
         <v>0</v>
       </c>
       <c r="W20">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>3.114224169723251</v>
+        <v>2.63025535980286</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09677542447470629</v>
+        <v>0.09781642447470629</v>
       </c>
       <c r="C21">
-        <v>351.8496056267493</v>
+        <v>339.0139835847684</v>
       </c>
       <c r="D21">
-        <v>403.5706056267493</v>
+        <v>395.4939835847684</v>
       </c>
       <c r="E21">
-        <v>58.42099999999999</v>
+        <v>63.18000000000001</v>
       </c>
       <c r="F21">
-        <v>90.42099999999999</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="G21">
         <v>38.7</v>
@@ -3003,45 +3003,45 @@
         <v>17.1</v>
       </c>
       <c r="M21">
-        <v>6.5012699</v>
+        <v>7.214644000000001</v>
       </c>
       <c r="N21">
-        <v>10.5987301</v>
+        <v>9.885356000000002</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>10.5987301</v>
+        <v>9.885356000000002</v>
       </c>
       <c r="Q21">
-        <v>14.0987301</v>
+        <v>13.385356</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1026104005860571</v>
+        <v>0.1033205305933829</v>
       </c>
       <c r="T21">
-        <v>1.107340448565258</v>
+        <v>1.121182204172324</v>
       </c>
       <c r="U21">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V21">
         <v>0</v>
       </c>
       <c r="W21">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y21">
-        <v>2.63025535980286</v>
+        <v>2.370179318619186</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09781642447470629</v>
+        <v>0.0981164244747063</v>
       </c>
       <c r="C22">
-        <v>339.0139835847684</v>
+        <v>331.9870878662298</v>
       </c>
       <c r="D22">
-        <v>395.4939835847684</v>
+        <v>393.2260878662299</v>
       </c>
       <c r="E22">
-        <v>63.18000000000001</v>
+        <v>67.93900000000001</v>
       </c>
       <c r="F22">
-        <v>95.18000000000001</v>
+        <v>99.93900000000001</v>
       </c>
       <c r="G22">
         <v>38.7</v>
@@ -3085,28 +3085,28 @@
         <v>17.1</v>
       </c>
       <c r="M22">
-        <v>7.214644000000001</v>
+        <v>7.575376200000001</v>
       </c>
       <c r="N22">
-        <v>9.885356000000002</v>
+        <v>9.524623800000001</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>9.885356000000002</v>
+        <v>9.524623800000001</v>
       </c>
       <c r="Q22">
-        <v>13.385356</v>
+        <v>13.0246238</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1033205305933829</v>
+        <v>0.1040486385755776</v>
       </c>
       <c r="T22">
-        <v>1.121182204172324</v>
+        <v>1.135374383971974</v>
       </c>
       <c r="U22">
         <v>0.07580000000000001</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.370179318619186</v>
+        <v>2.257313636780177</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0981164244747063</v>
+        <v>0.09841642447470628</v>
       </c>
       <c r="C23">
-        <v>331.9870878662299</v>
+        <v>324.9860536053012</v>
       </c>
       <c r="D23">
-        <v>393.2260878662299</v>
+        <v>390.9840536053011</v>
       </c>
       <c r="E23">
-        <v>67.93899999999999</v>
+        <v>72.69799999999999</v>
       </c>
       <c r="F23">
-        <v>99.93899999999999</v>
+        <v>104.698</v>
       </c>
       <c r="G23">
         <v>38.7</v>
@@ -3167,28 +3167,28 @@
         <v>17.1</v>
       </c>
       <c r="M23">
-        <v>7.5753762</v>
+        <v>7.9361084</v>
       </c>
       <c r="N23">
-        <v>9.524623800000001</v>
+        <v>9.163891600000001</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>9.524623800000001</v>
+        <v>9.163891600000001</v>
       </c>
       <c r="Q23">
-        <v>13.0246238</v>
+        <v>12.6638916</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1040486385755776</v>
+        <v>0.1047954159932132</v>
       </c>
       <c r="T23">
-        <v>1.135374383971974</v>
+        <v>1.149930465817768</v>
       </c>
       <c r="U23">
         <v>0.07580000000000001</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.257313636780177</v>
+        <v>2.154708471471988</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09841642447470628</v>
+        <v>0.0987164244747063</v>
       </c>
       <c r="C24">
-        <v>324.9860536053012</v>
+        <v>318.0104409515557</v>
       </c>
       <c r="D24">
-        <v>390.9840536053011</v>
+        <v>388.7674409515557</v>
       </c>
       <c r="E24">
-        <v>72.69799999999999</v>
+        <v>77.45699999999999</v>
       </c>
       <c r="F24">
-        <v>104.698</v>
+        <v>109.457</v>
       </c>
       <c r="G24">
         <v>38.7</v>
@@ -3249,28 +3249,28 @@
         <v>17.1</v>
       </c>
       <c r="M24">
-        <v>7.9361084</v>
+        <v>8.296840599999999</v>
       </c>
       <c r="N24">
-        <v>9.163891600000001</v>
+        <v>8.803159400000002</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>9.163891600000001</v>
+        <v>8.803159400000002</v>
       </c>
       <c r="Q24">
-        <v>12.6638916</v>
+        <v>12.3031594</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1047954159932132</v>
+        <v>0.1055615902268913</v>
       </c>
       <c r="T24">
-        <v>1.149930465817768</v>
+        <v>1.164864627711506</v>
       </c>
       <c r="U24">
         <v>0.07580000000000001</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.154708471471988</v>
+        <v>2.061025494451466</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0987164244747063</v>
+        <v>0.1024244244747063</v>
       </c>
       <c r="C25">
-        <v>318.0104409515557</v>
+        <v>287.7933513652802</v>
       </c>
       <c r="D25">
-        <v>388.7674409515557</v>
+        <v>363.3093513652802</v>
       </c>
       <c r="E25">
-        <v>77.45699999999999</v>
+        <v>82.21600000000001</v>
       </c>
       <c r="F25">
-        <v>109.457</v>
+        <v>114.216</v>
       </c>
       <c r="G25">
         <v>38.7</v>
@@ -3331,45 +3331,45 @@
         <v>17.1</v>
       </c>
       <c r="M25">
-        <v>8.296840599999999</v>
+        <v>10.27944</v>
       </c>
       <c r="N25">
-        <v>8.803159400000002</v>
+        <v>6.82056</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>8.803159400000002</v>
+        <v>6.82056</v>
       </c>
       <c r="Q25">
-        <v>12.3031594</v>
+        <v>10.32056</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1055615902268913</v>
+        <v>0.106347926940403</v>
       </c>
       <c r="T25">
-        <v>1.164864627711506</v>
+        <v>1.180191793865604</v>
       </c>
       <c r="U25">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V25">
         <v>0</v>
       </c>
       <c r="W25">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.061025494451466</v>
+        <v>1.663514743993836</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1024244244747063</v>
+        <v>0.1028664244747063</v>
       </c>
       <c r="C26">
-        <v>287.7933513652802</v>
+        <v>280.2203896569445</v>
       </c>
       <c r="D26">
-        <v>363.3093513652802</v>
+        <v>360.4953896569445</v>
       </c>
       <c r="E26">
-        <v>82.21599999999999</v>
+        <v>86.97499999999999</v>
       </c>
       <c r="F26">
-        <v>114.216</v>
+        <v>118.975</v>
       </c>
       <c r="G26">
         <v>38.7</v>
@@ -3413,28 +3413,28 @@
         <v>17.1</v>
       </c>
       <c r="M26">
-        <v>10.27944</v>
+        <v>10.70775</v>
       </c>
       <c r="N26">
-        <v>6.820560000000002</v>
+        <v>6.392250000000002</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>6.820560000000002</v>
+        <v>6.392250000000002</v>
       </c>
       <c r="Q26">
-        <v>10.32056</v>
+        <v>9.892250000000002</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.106347926940403</v>
+        <v>0.1071552326329417</v>
       </c>
       <c r="T26">
-        <v>1.180191793865604</v>
+        <v>1.195927684450479</v>
       </c>
       <c r="U26">
         <v>0.09</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>1.663514743993836</v>
+        <v>1.596974154234083</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1028664244747063</v>
+        <v>0.1033084244747063</v>
       </c>
       <c r="C27">
-        <v>280.2203896569445</v>
+        <v>272.6906832137789</v>
       </c>
       <c r="D27">
-        <v>360.4953896569445</v>
+        <v>357.7246832137789</v>
       </c>
       <c r="E27">
-        <v>86.97499999999999</v>
+        <v>91.73399999999999</v>
       </c>
       <c r="F27">
-        <v>118.975</v>
+        <v>123.734</v>
       </c>
       <c r="G27">
         <v>38.7</v>
@@ -3495,28 +3495,28 @@
         <v>17.1</v>
       </c>
       <c r="M27">
-        <v>10.70775</v>
+        <v>11.13606</v>
       </c>
       <c r="N27">
-        <v>6.392250000000002</v>
+        <v>5.963940000000003</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>6.392250000000002</v>
+        <v>5.963940000000003</v>
       </c>
       <c r="Q27">
-        <v>9.892250000000002</v>
+        <v>9.463940000000003</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1071552326329417</v>
+        <v>0.1079843573982517</v>
       </c>
       <c r="T27">
-        <v>1.195927684450479</v>
+        <v>1.212088869375485</v>
       </c>
       <c r="U27">
         <v>0.09</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>1.596974154234083</v>
+        <v>1.535552071378926</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1033084244747063</v>
+        <v>0.1190864244747063</v>
       </c>
       <c r="C28">
-        <v>272.6906832137789</v>
+        <v>190.9163274749407</v>
       </c>
       <c r="D28">
-        <v>357.7246832137789</v>
+        <v>280.7093274749407</v>
       </c>
       <c r="E28">
-        <v>91.73399999999999</v>
+        <v>96.49299999999999</v>
       </c>
       <c r="F28">
-        <v>123.734</v>
+        <v>128.493</v>
       </c>
       <c r="G28">
         <v>38.7</v>
@@ -3577,45 +3577,45 @@
         <v>17.1</v>
       </c>
       <c r="M28">
-        <v>11.13606</v>
+        <v>18.8627724</v>
       </c>
       <c r="N28">
-        <v>5.963940000000003</v>
+        <v>-1.762772399999999</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P28">
-        <v>5.963940000000003</v>
+        <v>-1.762772399999999</v>
       </c>
       <c r="Q28">
-        <v>9.463940000000003</v>
+        <v>1.737227600000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1079843573982517</v>
+        <v>0.1088361979105566</v>
       </c>
       <c r="T28">
-        <v>1.212088869375485</v>
+        <v>1.228692826490218</v>
       </c>
       <c r="U28">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V28">
         <v>0</v>
       </c>
       <c r="W28">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y28">
-        <v>1.535552071378926</v>
+        <v>0.90654754441081</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1190864244747063</v>
+        <v>0.1200964244747063</v>
       </c>
       <c r="C29">
-        <v>190.9163274749407</v>
+        <v>182.3413104491656</v>
       </c>
       <c r="D29">
-        <v>280.7093274749407</v>
+        <v>276.8933104491657</v>
       </c>
       <c r="E29">
-        <v>96.49299999999999</v>
+        <v>101.252</v>
       </c>
       <c r="F29">
-        <v>128.493</v>
+        <v>133.252</v>
       </c>
       <c r="G29">
         <v>38.7</v>
@@ -3659,28 +3659,28 @@
         <v>17.1</v>
       </c>
       <c r="M29">
-        <v>18.8627724</v>
+        <v>19.5613936</v>
       </c>
       <c r="N29">
-        <v>-1.762772399999999</v>
+        <v>-2.461393600000001</v>
       </c>
       <c r="O29">
         <v>-0</v>
       </c>
       <c r="P29">
-        <v>-1.762772399999999</v>
+        <v>-2.461393600000001</v>
       </c>
       <c r="Q29">
-        <v>1.737227600000001</v>
+        <v>1.038606399999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1088361979105566</v>
+        <v>0.1097117006593143</v>
       </c>
       <c r="T29">
-        <v>1.228692826490218</v>
+        <v>1.245758004635916</v>
       </c>
       <c r="U29">
         <v>0.1468</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.90654754441081</v>
+        <v>0.8741708463961382</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1200964244747063</v>
+        <v>0.1211064244747063</v>
       </c>
       <c r="C30">
-        <v>182.3413104491656</v>
+        <v>173.8686532744369</v>
       </c>
       <c r="D30">
-        <v>276.8933104491657</v>
+        <v>273.1796532744369</v>
       </c>
       <c r="E30">
-        <v>101.252</v>
+        <v>106.011</v>
       </c>
       <c r="F30">
-        <v>133.252</v>
+        <v>138.011</v>
       </c>
       <c r="G30">
         <v>38.7</v>
@@ -3741,28 +3741,28 @@
         <v>17.1</v>
       </c>
       <c r="M30">
-        <v>19.5613936</v>
+        <v>20.2600148</v>
       </c>
       <c r="N30">
-        <v>-2.461393600000001</v>
+        <v>-3.160014800000003</v>
       </c>
       <c r="O30">
         <v>-0</v>
       </c>
       <c r="P30">
-        <v>-2.461393600000001</v>
+        <v>-3.160014800000003</v>
       </c>
       <c r="Q30">
-        <v>1.038606399999999</v>
+        <v>0.3399851999999974</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1097117006593143</v>
+        <v>0.1106118654573328</v>
       </c>
       <c r="T30">
-        <v>1.245758004635916</v>
+        <v>1.263303892025154</v>
       </c>
       <c r="U30">
         <v>0.1468</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.8741708463961382</v>
+        <v>0.8440270241066161</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1211064244747063</v>
+        <v>0.1221164244747063</v>
       </c>
       <c r="C31">
-        <v>173.868653274437</v>
+        <v>165.4942919455185</v>
       </c>
       <c r="D31">
-        <v>273.179653274437</v>
+        <v>269.5642919455185</v>
       </c>
       <c r="E31">
-        <v>106.011</v>
+        <v>110.77</v>
       </c>
       <c r="F31">
-        <v>138.011</v>
+        <v>142.77</v>
       </c>
       <c r="G31">
         <v>38.7</v>
@@ -3823,28 +3823,28 @@
         <v>17.1</v>
       </c>
       <c r="M31">
-        <v>20.2600148</v>
+        <v>20.958636</v>
       </c>
       <c r="N31">
-        <v>-3.160014799999999</v>
+        <v>-3.858635999999997</v>
       </c>
       <c r="O31">
         <v>-0</v>
       </c>
       <c r="P31">
-        <v>-3.160014799999999</v>
+        <v>-3.858635999999997</v>
       </c>
       <c r="Q31">
-        <v>0.339985200000001</v>
+        <v>-0.3586359999999971</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1106118654573328</v>
+        <v>0.1115377492495804</v>
       </c>
       <c r="T31">
-        <v>1.263303892025154</v>
+        <v>1.281351090482656</v>
       </c>
       <c r="U31">
         <v>0.1468</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.8440270241066162</v>
+        <v>0.815892789969729</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1221164244747063</v>
+        <v>0.1398664244747063</v>
       </c>
       <c r="C32">
-        <v>165.4942919455185</v>
+        <v>109.8694680476458</v>
       </c>
       <c r="D32">
-        <v>269.5642919455185</v>
+        <v>218.6984680476458</v>
       </c>
       <c r="E32">
-        <v>110.77</v>
+        <v>115.529</v>
       </c>
       <c r="F32">
-        <v>142.77</v>
+        <v>147.529</v>
       </c>
       <c r="G32">
         <v>38.7</v>
@@ -3905,45 +3905,45 @@
         <v>17.1</v>
       </c>
       <c r="M32">
-        <v>20.958636</v>
+        <v>29.6238232</v>
       </c>
       <c r="N32">
-        <v>-3.858635999999997</v>
+        <v>-12.5238232</v>
       </c>
       <c r="O32">
         <v>-0</v>
       </c>
       <c r="P32">
-        <v>-3.858635999999997</v>
+        <v>-12.5238232</v>
       </c>
       <c r="Q32">
-        <v>-0.3586359999999971</v>
+        <v>-9.023823199999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1115377492495804</v>
+        <v>0.1124904702531975</v>
       </c>
       <c r="T32">
-        <v>1.281351090482656</v>
+        <v>1.299921396141825</v>
       </c>
       <c r="U32">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V32">
         <v>0</v>
       </c>
       <c r="W32">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y32">
-        <v>0.815892789969729</v>
+        <v>0.5772381196225882</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1398664244747063</v>
+        <v>0.1414164244747063</v>
       </c>
       <c r="C33">
-        <v>109.8694680476458</v>
+        <v>101.5652337708347</v>
       </c>
       <c r="D33">
-        <v>218.6984680476458</v>
+        <v>215.1532337708346</v>
       </c>
       <c r="E33">
-        <v>115.529</v>
+        <v>120.288</v>
       </c>
       <c r="F33">
-        <v>147.529</v>
+        <v>152.288</v>
       </c>
       <c r="G33">
         <v>38.7</v>
@@ -3987,28 +3987,28 @@
         <v>17.1</v>
       </c>
       <c r="M33">
-        <v>29.6238232</v>
+        <v>30.5794304</v>
       </c>
       <c r="N33">
-        <v>-12.5238232</v>
+        <v>-13.47943039999999</v>
       </c>
       <c r="O33">
         <v>-0</v>
       </c>
       <c r="P33">
-        <v>-12.5238232</v>
+        <v>-13.47943039999999</v>
       </c>
       <c r="Q33">
-        <v>-9.023823199999999</v>
+        <v>-9.979430399999995</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1124904702531975</v>
+        <v>0.1134712124628034</v>
       </c>
       <c r="T33">
-        <v>1.299921396141825</v>
+        <v>1.319037887261558</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.5772381196225882</v>
+        <v>0.5591994283843823</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1414164244747063</v>
+        <v>0.1429664244747063</v>
       </c>
       <c r="C34">
-        <v>101.5652337708347</v>
+        <v>93.37410673572279</v>
       </c>
       <c r="D34">
-        <v>215.1532337708346</v>
+        <v>211.7211067357228</v>
       </c>
       <c r="E34">
-        <v>120.288</v>
+        <v>125.047</v>
       </c>
       <c r="F34">
-        <v>152.288</v>
+        <v>157.047</v>
       </c>
       <c r="G34">
         <v>38.7</v>
@@ -4069,28 +4069,28 @@
         <v>17.1</v>
       </c>
       <c r="M34">
-        <v>30.5794304</v>
+        <v>31.5350376</v>
       </c>
       <c r="N34">
-        <v>-13.47943039999999</v>
+        <v>-14.4350376</v>
       </c>
       <c r="O34">
         <v>-0</v>
       </c>
       <c r="P34">
-        <v>-13.47943039999999</v>
+        <v>-14.4350376</v>
       </c>
       <c r="Q34">
-        <v>-9.979430399999995</v>
+        <v>-10.9350376</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1134712124628034</v>
+        <v>0.1144812305592631</v>
       </c>
       <c r="T34">
-        <v>1.319037887261558</v>
+        <v>1.338725019907253</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.5591994283843823</v>
+        <v>0.5422539911606131</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1429664244747063</v>
+        <v>0.1445164244747063</v>
       </c>
       <c r="C35">
-        <v>93.37410673572279</v>
+        <v>85.29075906828419</v>
       </c>
       <c r="D35">
-        <v>211.7211067357228</v>
+        <v>208.3967590682842</v>
       </c>
       <c r="E35">
-        <v>125.047</v>
+        <v>129.806</v>
       </c>
       <c r="F35">
-        <v>157.047</v>
+        <v>161.806</v>
       </c>
       <c r="G35">
         <v>38.7</v>
@@ -4151,28 +4151,28 @@
         <v>17.1</v>
       </c>
       <c r="M35">
-        <v>31.5350376</v>
+        <v>32.49064480000001</v>
       </c>
       <c r="N35">
-        <v>-14.4350376</v>
+        <v>-15.3906448</v>
       </c>
       <c r="O35">
         <v>-0</v>
       </c>
       <c r="P35">
-        <v>-14.4350376</v>
+        <v>-15.3906448</v>
       </c>
       <c r="Q35">
-        <v>-10.9350376</v>
+        <v>-11.8906448</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1144812305592631</v>
+        <v>0.1155218552647065</v>
       </c>
       <c r="T35">
-        <v>1.338725019907253</v>
+        <v>1.35900873233009</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.5422539911606131</v>
+        <v>0.5263053443617715</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1445164244747063</v>
+        <v>0.1460664244747063</v>
       </c>
       <c r="C36">
-        <v>85.29075906828419</v>
+        <v>77.31019234494568</v>
       </c>
       <c r="D36">
-        <v>208.3967590682842</v>
+        <v>205.1751923449457</v>
       </c>
       <c r="E36">
-        <v>129.806</v>
+        <v>134.565</v>
       </c>
       <c r="F36">
-        <v>161.806</v>
+        <v>166.565</v>
       </c>
       <c r="G36">
         <v>38.7</v>
@@ -4233,28 +4233,28 @@
         <v>17.1</v>
       </c>
       <c r="M36">
-        <v>32.49064480000001</v>
+        <v>33.446252</v>
       </c>
       <c r="N36">
-        <v>-15.3906448</v>
+        <v>-16.346252</v>
       </c>
       <c r="O36">
         <v>-0</v>
       </c>
       <c r="P36">
-        <v>-15.3906448</v>
+        <v>-16.346252</v>
       </c>
       <c r="Q36">
-        <v>-11.8906448</v>
+        <v>-12.846252</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1155218552647065</v>
+        <v>0.1165944991918558</v>
       </c>
       <c r="T36">
-        <v>1.35900873233009</v>
+        <v>1.379916558981322</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.5263053443617715</v>
+        <v>0.511268048808578</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1460664244747063</v>
+        <v>0.1602164244747063</v>
       </c>
       <c r="C37">
-        <v>77.31019234494568</v>
+        <v>47.17695971173845</v>
       </c>
       <c r="D37">
-        <v>205.1751923449457</v>
+        <v>179.8009597117385</v>
       </c>
       <c r="E37">
-        <v>134.565</v>
+        <v>139.324</v>
       </c>
       <c r="F37">
-        <v>166.565</v>
+        <v>171.324</v>
       </c>
       <c r="G37">
         <v>38.7</v>
@@ -4315,45 +4315,45 @@
         <v>17.1</v>
       </c>
       <c r="M37">
-        <v>33.446252</v>
+        <v>40.39819920000001</v>
       </c>
       <c r="N37">
-        <v>-16.346252</v>
+        <v>-23.29819920000001</v>
       </c>
       <c r="O37">
         <v>-0</v>
       </c>
       <c r="P37">
-        <v>-16.346252</v>
+        <v>-23.29819920000001</v>
       </c>
       <c r="Q37">
-        <v>-12.846252</v>
+        <v>-19.79819920000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1165944991918558</v>
+        <v>0.1177006632417286</v>
       </c>
       <c r="T37">
-        <v>1.379916558981322</v>
+        <v>1.401477755215405</v>
       </c>
       <c r="U37">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V37">
         <v>0</v>
       </c>
       <c r="W37">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y37">
-        <v>0.511268048808578</v>
+        <v>0.4232861944004672</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1602164244747063</v>
+        <v>0.1621164244747063</v>
       </c>
       <c r="C38">
-        <v>47.17695971173848</v>
+        <v>39.48095554405458</v>
       </c>
       <c r="D38">
-        <v>179.8009597117385</v>
+        <v>176.8639555440546</v>
       </c>
       <c r="E38">
-        <v>139.324</v>
+        <v>144.083</v>
       </c>
       <c r="F38">
-        <v>171.324</v>
+        <v>176.083</v>
       </c>
       <c r="G38">
         <v>38.7</v>
@@ -4397,28 +4397,28 @@
         <v>17.1</v>
       </c>
       <c r="M38">
-        <v>40.3981992</v>
+        <v>41.5203714</v>
       </c>
       <c r="N38">
-        <v>-23.2981992</v>
+        <v>-24.4203714</v>
       </c>
       <c r="O38">
         <v>-0</v>
       </c>
       <c r="P38">
-        <v>-23.2981992</v>
+        <v>-24.4203714</v>
       </c>
       <c r="Q38">
-        <v>-19.7981992</v>
+        <v>-20.9203714</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1177006632417286</v>
+        <v>0.1188419436106449</v>
       </c>
       <c r="T38">
-        <v>1.401477755215405</v>
+        <v>1.423723433869618</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.4232861944004672</v>
+        <v>0.4118460269842384</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1621164244747063</v>
+        <v>0.1640164244747063</v>
       </c>
       <c r="C39">
-        <v>39.48095554405458</v>
+        <v>31.87935971164893</v>
       </c>
       <c r="D39">
-        <v>176.8639555440546</v>
+        <v>174.0213597116489</v>
       </c>
       <c r="E39">
-        <v>144.083</v>
+        <v>148.842</v>
       </c>
       <c r="F39">
-        <v>176.083</v>
+        <v>180.842</v>
       </c>
       <c r="G39">
         <v>38.7</v>
@@ -4479,28 +4479,28 @@
         <v>17.1</v>
       </c>
       <c r="M39">
-        <v>41.5203714</v>
+        <v>42.6425436</v>
       </c>
       <c r="N39">
-        <v>-24.4203714</v>
+        <v>-25.54254359999999</v>
       </c>
       <c r="O39">
         <v>-0</v>
       </c>
       <c r="P39">
-        <v>-24.4203714</v>
+        <v>-25.54254359999999</v>
       </c>
       <c r="Q39">
-        <v>-20.9203714</v>
+        <v>-22.04254359999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1188419436106449</v>
+        <v>0.1200200394753327</v>
       </c>
       <c r="T39">
-        <v>1.423723433869618</v>
+        <v>1.446686715061063</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.4118460269842384</v>
+        <v>0.401007973642548</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1640164244747063</v>
+        <v>0.1659164244747063</v>
       </c>
       <c r="C40">
-        <v>31.87935971164893</v>
+        <v>24.36769216515728</v>
       </c>
       <c r="D40">
-        <v>174.0213597116489</v>
+        <v>171.2686921651573</v>
       </c>
       <c r="E40">
-        <v>148.842</v>
+        <v>153.601</v>
       </c>
       <c r="F40">
-        <v>180.842</v>
+        <v>185.601</v>
       </c>
       <c r="G40">
         <v>38.7</v>
@@ -4561,28 +4561,28 @@
         <v>17.1</v>
       </c>
       <c r="M40">
-        <v>42.6425436</v>
+        <v>43.7647158</v>
       </c>
       <c r="N40">
-        <v>-25.54254359999999</v>
+        <v>-26.6647158</v>
       </c>
       <c r="O40">
         <v>-0</v>
       </c>
       <c r="P40">
-        <v>-25.54254359999999</v>
+        <v>-26.6647158</v>
       </c>
       <c r="Q40">
-        <v>-22.04254359999999</v>
+        <v>-23.1647158</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1200200394753327</v>
+        <v>0.1212367614339447</v>
       </c>
       <c r="T40">
-        <v>1.446686715061063</v>
+        <v>1.470402890717802</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.401007973642548</v>
+        <v>0.3907257179081236</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1659164244747063</v>
+        <v>0.1678164244747063</v>
       </c>
       <c r="C41">
-        <v>24.36769216515728</v>
+        <v>16.94175190269073</v>
       </c>
       <c r="D41">
-        <v>171.2686921651573</v>
+        <v>168.6017519026908</v>
       </c>
       <c r="E41">
-        <v>153.601</v>
+        <v>158.36</v>
       </c>
       <c r="F41">
-        <v>185.601</v>
+        <v>190.36</v>
       </c>
       <c r="G41">
         <v>38.7</v>
@@ -4643,28 +4643,28 @@
         <v>17.1</v>
       </c>
       <c r="M41">
-        <v>43.7647158</v>
+        <v>44.88688800000001</v>
       </c>
       <c r="N41">
-        <v>-26.6647158</v>
+        <v>-27.786888</v>
       </c>
       <c r="O41">
         <v>-0</v>
       </c>
       <c r="P41">
-        <v>-26.6647158</v>
+        <v>-27.786888</v>
       </c>
       <c r="Q41">
-        <v>-23.1647158</v>
+        <v>-24.286888</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1212367614339447</v>
+        <v>0.1224940407911772</v>
       </c>
       <c r="T41">
-        <v>1.470402890717802</v>
+        <v>1.494909605563099</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3907257179081236</v>
+        <v>0.3809575749604205</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1678164244747063</v>
+        <v>0.1697164244747063</v>
       </c>
       <c r="C42">
-        <v>16.94175190269073</v>
+        <v>9.597595576779355</v>
       </c>
       <c r="D42">
-        <v>168.6017519026908</v>
+        <v>166.0165955767794</v>
       </c>
       <c r="E42">
-        <v>158.36</v>
+        <v>163.119</v>
       </c>
       <c r="F42">
-        <v>190.36</v>
+        <v>195.119</v>
       </c>
       <c r="G42">
         <v>38.7</v>
@@ -4725,28 +4725,28 @@
         <v>17.1</v>
       </c>
       <c r="M42">
-        <v>44.88688800000001</v>
+        <v>46.0090602</v>
       </c>
       <c r="N42">
-        <v>-27.786888</v>
+        <v>-28.9090602</v>
       </c>
       <c r="O42">
         <v>-0</v>
       </c>
       <c r="P42">
-        <v>-27.786888</v>
+        <v>-28.9090602</v>
       </c>
       <c r="Q42">
-        <v>-24.286888</v>
+        <v>-25.4090602</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1224940407911772</v>
+        <v>0.1237939397876378</v>
       </c>
       <c r="T42">
-        <v>1.494909605563099</v>
+        <v>1.520247056504846</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3809575749604205</v>
+        <v>0.3716659267906541</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1697164244747063</v>
+        <v>0.1716164244747063</v>
       </c>
       <c r="C43">
-        <v>9.597595576779355</v>
+        <v>2.331518039702331</v>
       </c>
       <c r="D43">
-        <v>166.0165955767794</v>
+        <v>163.5095180397023</v>
       </c>
       <c r="E43">
-        <v>163.119</v>
+        <v>167.878</v>
       </c>
       <c r="F43">
-        <v>195.119</v>
+        <v>199.878</v>
       </c>
       <c r="G43">
         <v>38.7</v>
@@ -4807,28 +4807,28 @@
         <v>17.1</v>
       </c>
       <c r="M43">
-        <v>46.0090602</v>
+        <v>47.1312324</v>
       </c>
       <c r="N43">
-        <v>-28.9090602</v>
+        <v>-30.0312324</v>
       </c>
       <c r="O43">
         <v>-0</v>
       </c>
       <c r="P43">
-        <v>-28.9090602</v>
+        <v>-30.0312324</v>
       </c>
       <c r="Q43">
-        <v>-25.4090602</v>
+        <v>-26.5312324</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1237939397876378</v>
+        <v>0.1251386628874246</v>
       </c>
       <c r="T43">
-        <v>1.520247056504846</v>
+        <v>1.546458212651482</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3716659267906541</v>
+        <v>0.3628167380575433</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1716164244747063</v>
+        <v>0.1735164244747063</v>
       </c>
       <c r="C44">
-        <v>2.33151803970236</v>
+        <v>-4.859965374652575</v>
       </c>
       <c r="D44">
-        <v>163.5095180397023</v>
+        <v>161.0770346253474</v>
       </c>
       <c r="E44">
-        <v>167.878</v>
+        <v>172.637</v>
       </c>
       <c r="F44">
-        <v>199.878</v>
+        <v>204.637</v>
       </c>
       <c r="G44">
         <v>38.7</v>
@@ -4889,28 +4889,28 @@
         <v>17.1</v>
       </c>
       <c r="M44">
-        <v>47.1312324</v>
+        <v>48.2534046</v>
       </c>
       <c r="N44">
-        <v>-30.0312324</v>
+        <v>-31.1534046</v>
       </c>
       <c r="O44">
         <v>-0</v>
       </c>
       <c r="P44">
-        <v>-30.0312324</v>
+        <v>-31.1534046</v>
       </c>
       <c r="Q44">
-        <v>-26.5312324</v>
+        <v>-27.6534046</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1251386628874246</v>
+        <v>0.1265305692538707</v>
       </c>
       <c r="T44">
-        <v>1.546458212651481</v>
+        <v>1.573589058487472</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3628167380575433</v>
+        <v>0.3543791394980657</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1735164244747063</v>
+        <v>0.1754164244747063</v>
       </c>
       <c r="C45">
-        <v>-4.859965374652575</v>
+        <v>-11.9801350105877</v>
       </c>
       <c r="D45">
-        <v>161.0770346253474</v>
+        <v>158.7158649894123</v>
       </c>
       <c r="E45">
-        <v>172.637</v>
+        <v>177.396</v>
       </c>
       <c r="F45">
-        <v>204.637</v>
+        <v>209.396</v>
       </c>
       <c r="G45">
         <v>38.7</v>
@@ -4971,28 +4971,28 @@
         <v>17.1</v>
       </c>
       <c r="M45">
-        <v>48.2534046</v>
+        <v>49.3755768</v>
       </c>
       <c r="N45">
-        <v>-31.1534046</v>
+        <v>-32.2755768</v>
       </c>
       <c r="O45">
         <v>-0</v>
       </c>
       <c r="P45">
-        <v>-31.1534046</v>
+        <v>-32.2755768</v>
       </c>
       <c r="Q45">
-        <v>-27.6534046</v>
+        <v>-28.7755768</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1265305692538707</v>
+        <v>0.1279721865619755</v>
       </c>
       <c r="T45">
-        <v>1.573589058487472</v>
+        <v>1.60168886310332</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3543791394980657</v>
+        <v>0.3463250681458369</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1754164244747063</v>
+        <v>0.1773164244747063</v>
       </c>
       <c r="C46">
-        <v>-11.9801350105877</v>
+        <v>-19.03208164964329</v>
       </c>
       <c r="D46">
-        <v>158.7158649894123</v>
+        <v>156.4229183503567</v>
       </c>
       <c r="E46">
-        <v>177.396</v>
+        <v>182.155</v>
       </c>
       <c r="F46">
-        <v>209.396</v>
+        <v>214.155</v>
       </c>
       <c r="G46">
         <v>38.7</v>
@@ -5053,28 +5053,28 @@
         <v>17.1</v>
       </c>
       <c r="M46">
-        <v>49.3755768</v>
+        <v>50.497749</v>
       </c>
       <c r="N46">
-        <v>-32.2755768</v>
+        <v>-33.397749</v>
       </c>
       <c r="O46">
         <v>-0</v>
       </c>
       <c r="P46">
-        <v>-32.2755768</v>
+        <v>-33.397749</v>
       </c>
       <c r="Q46">
-        <v>-28.7755768</v>
+        <v>-29.897749</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1279721865619755</v>
+        <v>0.1294662263176478</v>
       </c>
       <c r="T46">
-        <v>1.60168886310332</v>
+        <v>1.630810478796108</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3463250681458369</v>
+        <v>0.3386289555203739</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1773164244747063</v>
+        <v>0.1792164244747063</v>
       </c>
       <c r="C47">
-        <v>-19.03208164964329</v>
+        <v>-26.01872000853234</v>
       </c>
       <c r="D47">
-        <v>156.4229183503567</v>
+        <v>154.1952799914677</v>
       </c>
       <c r="E47">
-        <v>182.155</v>
+        <v>186.914</v>
       </c>
       <c r="F47">
-        <v>214.155</v>
+        <v>218.914</v>
       </c>
       <c r="G47">
         <v>38.7</v>
@@ -5135,28 +5135,28 @@
         <v>17.1</v>
       </c>
       <c r="M47">
-        <v>50.497749</v>
+        <v>51.6199212</v>
       </c>
       <c r="N47">
-        <v>-33.397749</v>
+        <v>-34.5199212</v>
       </c>
       <c r="O47">
         <v>-0</v>
       </c>
       <c r="P47">
-        <v>-33.397749</v>
+        <v>-34.5199212</v>
       </c>
       <c r="Q47">
-        <v>-29.897749</v>
+        <v>-31.0199212</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1294662263176478</v>
+        <v>0.1310156008790857</v>
       </c>
       <c r="T47">
-        <v>1.630810478796108</v>
+        <v>1.661010672847888</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3386289555203739</v>
+        <v>0.3312674564873223</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1792164244747063</v>
+        <v>0.1811164244747063</v>
       </c>
       <c r="C48">
-        <v>-26.01872000853234</v>
+        <v>-32.9428010999157</v>
       </c>
       <c r="D48">
-        <v>154.1952799914677</v>
+        <v>152.0301989000843</v>
       </c>
       <c r="E48">
-        <v>186.914</v>
+        <v>191.673</v>
       </c>
       <c r="F48">
-        <v>218.914</v>
+        <v>223.673</v>
       </c>
       <c r="G48">
         <v>38.7</v>
@@ -5217,28 +5217,28 @@
         <v>17.1</v>
       </c>
       <c r="M48">
-        <v>51.6199212</v>
+        <v>52.7420934</v>
       </c>
       <c r="N48">
-        <v>-34.5199212</v>
+        <v>-35.6420934</v>
       </c>
       <c r="O48">
         <v>-0</v>
       </c>
       <c r="P48">
-        <v>-34.5199212</v>
+        <v>-35.6420934</v>
       </c>
       <c r="Q48">
-        <v>-31.0199212</v>
+        <v>-32.1420934</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1310156008790857</v>
+        <v>0.1326234424051062</v>
       </c>
       <c r="T48">
-        <v>1.661010672847888</v>
+        <v>1.692350496863885</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3312674564873223</v>
+        <v>0.3242192127322728</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1811164244747063</v>
+        <v>0.1830164244747063</v>
       </c>
       <c r="C49">
-        <v>-32.9428010999157</v>
+        <v>-39.80692356623831</v>
       </c>
       <c r="D49">
-        <v>152.0301989000843</v>
+        <v>149.9250764337617</v>
       </c>
       <c r="E49">
-        <v>191.673</v>
+        <v>196.432</v>
       </c>
       <c r="F49">
-        <v>223.673</v>
+        <v>228.432</v>
       </c>
       <c r="G49">
         <v>38.7</v>
@@ -5299,28 +5299,28 @@
         <v>17.1</v>
       </c>
       <c r="M49">
-        <v>52.7420934</v>
+        <v>53.8642656</v>
       </c>
       <c r="N49">
-        <v>-35.6420934</v>
+        <v>-36.7642656</v>
       </c>
       <c r="O49">
         <v>-0</v>
       </c>
       <c r="P49">
-        <v>-35.6420934</v>
+        <v>-36.7642656</v>
       </c>
       <c r="Q49">
-        <v>-32.1420934</v>
+        <v>-33.2642656</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1326234424051062</v>
+        <v>0.1342931239898198</v>
       </c>
       <c r="T49">
-        <v>1.692350496863885</v>
+        <v>1.724895698726652</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3242192127322728</v>
+        <v>0.3174646458003504</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1830164244747063</v>
+        <v>0.1849164244747063</v>
       </c>
       <c r="C50">
-        <v>-39.80692356623828</v>
+        <v>-46.61354408480571</v>
       </c>
       <c r="D50">
-        <v>149.9250764337617</v>
+        <v>147.8774559151943</v>
       </c>
       <c r="E50">
-        <v>196.432</v>
+        <v>201.191</v>
       </c>
       <c r="F50">
-        <v>228.432</v>
+        <v>233.191</v>
       </c>
       <c r="G50">
         <v>38.7</v>
@@ -5381,28 +5381,28 @@
         <v>17.1</v>
       </c>
       <c r="M50">
-        <v>53.8642656</v>
+        <v>54.9864378</v>
       </c>
       <c r="N50">
-        <v>-36.76426559999999</v>
+        <v>-37.8864378</v>
       </c>
       <c r="O50">
         <v>-0</v>
       </c>
       <c r="P50">
-        <v>-36.76426559999999</v>
+        <v>-37.8864378</v>
       </c>
       <c r="Q50">
-        <v>-33.26426559999999</v>
+        <v>-34.3864378</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1342931239898198</v>
+        <v>0.1360282832837378</v>
       </c>
       <c r="T50">
-        <v>1.724895698726652</v>
+        <v>1.75871718301541</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3174646458003505</v>
+        <v>0.3109857754778943</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1849164244747063</v>
+        <v>0.1868164244747063</v>
       </c>
       <c r="C51">
-        <v>-46.61354408480571</v>
+        <v>-53.36498693169733</v>
       </c>
       <c r="D51">
-        <v>147.8774559151943</v>
+        <v>145.8850130683026</v>
       </c>
       <c r="E51">
-        <v>201.191</v>
+        <v>205.95</v>
       </c>
       <c r="F51">
-        <v>233.191</v>
+        <v>237.95</v>
       </c>
       <c r="G51">
         <v>38.7</v>
@@ -5463,28 +5463,28 @@
         <v>17.1</v>
       </c>
       <c r="M51">
-        <v>54.9864378</v>
+        <v>56.10861</v>
       </c>
       <c r="N51">
-        <v>-37.8864378</v>
+        <v>-39.00861</v>
       </c>
       <c r="O51">
         <v>-0</v>
       </c>
       <c r="P51">
-        <v>-37.8864378</v>
+        <v>-39.00861</v>
       </c>
       <c r="Q51">
-        <v>-34.3864378</v>
+        <v>-35.50861</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1360282832837378</v>
+        <v>0.1378328489494126</v>
       </c>
       <c r="T51">
-        <v>1.75871718301541</v>
+        <v>1.793891526675718</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3109857754778943</v>
+        <v>0.3047660599683364</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1868164244747063</v>
+        <v>0.1887164244747063</v>
       </c>
       <c r="C52">
-        <v>-53.36498693169733</v>
+        <v>-60.06345278279576</v>
       </c>
       <c r="D52">
-        <v>145.8850130683026</v>
+        <v>143.9455472172043</v>
       </c>
       <c r="E52">
-        <v>205.95</v>
+        <v>210.709</v>
       </c>
       <c r="F52">
-        <v>237.95</v>
+        <v>242.709</v>
       </c>
       <c r="G52">
         <v>38.7</v>
@@ -5545,28 +5545,28 @@
         <v>17.1</v>
       </c>
       <c r="M52">
-        <v>56.10861</v>
+        <v>57.2307822</v>
       </c>
       <c r="N52">
-        <v>-39.00861</v>
+        <v>-40.1307822</v>
       </c>
       <c r="O52">
         <v>-0</v>
       </c>
       <c r="P52">
-        <v>-39.00861</v>
+        <v>-40.1307822</v>
       </c>
       <c r="Q52">
-        <v>-35.50861</v>
+        <v>-36.6307822</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1378328489494126</v>
+        <v>0.1397110703565434</v>
       </c>
       <c r="T52">
-        <v>1.793891526675718</v>
+        <v>1.830501557832366</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3047660599683364</v>
+        <v>0.298790254870918</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1887164244747063</v>
+        <v>0.1906164244747063</v>
       </c>
       <c r="C53">
-        <v>-60.06345278279576</v>
+        <v>-66.71102682199566</v>
       </c>
       <c r="D53">
-        <v>143.9455472172043</v>
+        <v>142.0569731780043</v>
       </c>
       <c r="E53">
-        <v>210.709</v>
+        <v>215.468</v>
       </c>
       <c r="F53">
-        <v>242.709</v>
+        <v>247.468</v>
       </c>
       <c r="G53">
         <v>38.7</v>
@@ -5627,28 +5627,28 @@
         <v>17.1</v>
       </c>
       <c r="M53">
-        <v>57.2307822</v>
+        <v>58.3529544</v>
       </c>
       <c r="N53">
-        <v>-40.1307822</v>
+        <v>-41.2529544</v>
       </c>
       <c r="O53">
         <v>-0</v>
       </c>
       <c r="P53">
-        <v>-40.1307822</v>
+        <v>-41.2529544</v>
       </c>
       <c r="Q53">
-        <v>-36.6307822</v>
+        <v>-37.7529544</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1397110703565434</v>
+        <v>0.1416675509889714</v>
       </c>
       <c r="T53">
-        <v>1.830501557832366</v>
+        <v>1.868637006953874</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.298790254870918</v>
+        <v>0.2930442884310928</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1906164244747063</v>
+        <v>0.1925164244747063</v>
       </c>
       <c r="C54">
-        <v>-66.71102682199566</v>
+        <v>-73.30968621939834</v>
       </c>
       <c r="D54">
-        <v>142.0569731780043</v>
+        <v>140.2173137806017</v>
       </c>
       <c r="E54">
-        <v>215.468</v>
+        <v>220.227</v>
       </c>
       <c r="F54">
-        <v>247.468</v>
+        <v>252.227</v>
       </c>
       <c r="G54">
         <v>38.7</v>
@@ -5709,28 +5709,28 @@
         <v>17.1</v>
       </c>
       <c r="M54">
-        <v>58.3529544</v>
+        <v>59.4751266</v>
       </c>
       <c r="N54">
-        <v>-41.2529544</v>
+        <v>-42.3751266</v>
       </c>
       <c r="O54">
         <v>-0</v>
       </c>
       <c r="P54">
-        <v>-41.2529544</v>
+        <v>-42.3751266</v>
       </c>
       <c r="Q54">
-        <v>-37.7529544</v>
+        <v>-38.8751266</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1416675509889714</v>
+        <v>0.1437072861163964</v>
       </c>
       <c r="T54">
-        <v>1.868637006953874</v>
+        <v>1.908395241144381</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2930442884310928</v>
+        <v>0.287515150913525</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1925164244747063</v>
+        <v>0.1944164244747063</v>
       </c>
       <c r="C55">
-        <v>-73.30968621939834</v>
+        <v>-79.86130703587133</v>
       </c>
       <c r="D55">
-        <v>140.2173137806017</v>
+        <v>138.4246929641287</v>
       </c>
       <c r="E55">
-        <v>220.227</v>
+        <v>224.986</v>
       </c>
       <c r="F55">
-        <v>252.227</v>
+        <v>256.986</v>
       </c>
       <c r="G55">
         <v>38.7</v>
@@ -5791,28 +5791,28 @@
         <v>17.1</v>
       </c>
       <c r="M55">
-        <v>59.4751266</v>
+        <v>60.5972988</v>
       </c>
       <c r="N55">
-        <v>-42.3751266</v>
+        <v>-43.4972988</v>
       </c>
       <c r="O55">
         <v>-0</v>
       </c>
       <c r="P55">
-        <v>-42.3751266</v>
+        <v>-43.4972988</v>
       </c>
       <c r="Q55">
-        <v>-38.8751266</v>
+        <v>-39.9972988</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1437072861163964</v>
+        <v>0.1458357053797963</v>
       </c>
       <c r="T55">
-        <v>1.908395241144381</v>
+        <v>1.949882094212737</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.287515150913525</v>
+        <v>0.2821907962669782</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1944164244747063</v>
+        <v>0.1963164244747063</v>
       </c>
       <c r="C56">
-        <v>-79.86130703587133</v>
+        <v>-86.36767060466275</v>
       </c>
       <c r="D56">
-        <v>138.4246929641287</v>
+        <v>136.6773293953372</v>
       </c>
       <c r="E56">
-        <v>224.986</v>
+        <v>229.745</v>
       </c>
       <c r="F56">
-        <v>256.986</v>
+        <v>261.745</v>
       </c>
       <c r="G56">
         <v>38.7</v>
@@ -5873,28 +5873,28 @@
         <v>17.1</v>
       </c>
       <c r="M56">
-        <v>60.5972988</v>
+        <v>61.71947100000001</v>
       </c>
       <c r="N56">
-        <v>-43.4972988</v>
+        <v>-44.619471</v>
       </c>
       <c r="O56">
         <v>-0</v>
       </c>
       <c r="P56">
-        <v>-43.4972988</v>
+        <v>-44.619471</v>
       </c>
       <c r="Q56">
-        <v>-39.9972988</v>
+        <v>-41.119471</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1458357053797963</v>
+        <v>0.1480587210549029</v>
       </c>
       <c r="T56">
-        <v>1.949882094212737</v>
+        <v>1.993212807417465</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2821907962669782</v>
+        <v>0.2770600545166695</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1963164244747063</v>
+        <v>0.1982164244747063</v>
       </c>
       <c r="C57">
-        <v>-86.36767060466275</v>
+        <v>-92.83046943570173</v>
       </c>
       <c r="D57">
-        <v>136.6773293953372</v>
+        <v>134.9735305642983</v>
       </c>
       <c r="E57">
-        <v>229.745</v>
+        <v>234.504</v>
       </c>
       <c r="F57">
-        <v>261.745</v>
+        <v>266.504</v>
       </c>
       <c r="G57">
         <v>38.7</v>
@@ -5955,28 +5955,28 @@
         <v>17.1</v>
       </c>
       <c r="M57">
-        <v>61.71947100000001</v>
+        <v>62.84164320000001</v>
       </c>
       <c r="N57">
-        <v>-44.619471</v>
+        <v>-45.74164320000001</v>
       </c>
       <c r="O57">
         <v>-0</v>
       </c>
       <c r="P57">
-        <v>-44.619471</v>
+        <v>-45.74164320000001</v>
       </c>
       <c r="Q57">
-        <v>-41.119471</v>
+        <v>-42.24164320000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1480587210549029</v>
+        <v>0.1503827828970597</v>
       </c>
       <c r="T57">
-        <v>1.993212807417465</v>
+        <v>2.038513098495135</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2770600545166695</v>
+        <v>0.2721125535431576</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1982164244747063</v>
+        <v>0.2001164244747063</v>
       </c>
       <c r="C58">
-        <v>-92.83046943570173</v>
+        <v>-99.2513126837236</v>
       </c>
       <c r="D58">
-        <v>134.9735305642983</v>
+        <v>133.3116873162764</v>
       </c>
       <c r="E58">
-        <v>234.504</v>
+        <v>239.263</v>
       </c>
       <c r="F58">
-        <v>266.504</v>
+        <v>271.263</v>
       </c>
       <c r="G58">
         <v>38.7</v>
@@ -6037,28 +6037,28 @@
         <v>17.1</v>
       </c>
       <c r="M58">
-        <v>62.84164320000001</v>
+        <v>63.96381540000001</v>
       </c>
       <c r="N58">
-        <v>-45.74164320000001</v>
+        <v>-46.86381540000001</v>
       </c>
       <c r="O58">
         <v>-0</v>
       </c>
       <c r="P58">
-        <v>-45.74164320000001</v>
+        <v>-46.86381540000001</v>
       </c>
       <c r="Q58">
-        <v>-42.24164320000001</v>
+        <v>-43.36381540000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1503827828970597</v>
+        <v>0.1528149406388518</v>
       </c>
       <c r="T58">
-        <v>2.038513098495135</v>
+        <v>2.085920379855487</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2721125535431576</v>
+        <v>0.2673386490950319</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2001164244747063</v>
+        <v>0.2020164244747063</v>
       </c>
       <c r="C59">
-        <v>-99.2513126837236</v>
+        <v>-105.631731217355</v>
       </c>
       <c r="D59">
-        <v>133.3116873162764</v>
+        <v>131.690268782645</v>
       </c>
       <c r="E59">
-        <v>239.263</v>
+        <v>244.022</v>
       </c>
       <c r="F59">
-        <v>271.263</v>
+        <v>276.022</v>
       </c>
       <c r="G59">
         <v>38.7</v>
@@ -6119,28 +6119,28 @@
         <v>17.1</v>
       </c>
       <c r="M59">
-        <v>63.96381540000001</v>
+        <v>65.08598760000001</v>
       </c>
       <c r="N59">
-        <v>-46.86381540000001</v>
+        <v>-47.98598760000001</v>
       </c>
       <c r="O59">
         <v>-0</v>
       </c>
       <c r="P59">
-        <v>-46.86381540000001</v>
+        <v>-47.98598760000001</v>
       </c>
       <c r="Q59">
-        <v>-43.36381540000001</v>
+        <v>-44.48598760000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1528149406388518</v>
+        <v>0.1553629154159674</v>
       </c>
       <c r="T59">
-        <v>2.085920379855487</v>
+        <v>2.135585150804427</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2673386490950319</v>
+        <v>0.2627293620416693</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2020164244747063</v>
+        <v>0.2039164244747063</v>
       </c>
       <c r="C60">
-        <v>-105.631731217355</v>
+        <v>-111.9731823227241</v>
       </c>
       <c r="D60">
-        <v>131.690268782645</v>
+        <v>130.1078176772758</v>
       </c>
       <c r="E60">
-        <v>244.022</v>
+        <v>248.7809999999999</v>
       </c>
       <c r="F60">
-        <v>276.022</v>
+        <v>280.7809999999999</v>
       </c>
       <c r="G60">
         <v>38.7</v>
@@ -6201,28 +6201,28 @@
         <v>17.1</v>
       </c>
       <c r="M60">
-        <v>65.0859876</v>
+        <v>66.20815979999999</v>
       </c>
       <c r="N60">
-        <v>-47.98598759999999</v>
+        <v>-49.10815979999999</v>
       </c>
       <c r="O60">
         <v>-0</v>
       </c>
       <c r="P60">
-        <v>-47.98598759999999</v>
+        <v>-49.10815979999999</v>
       </c>
       <c r="Q60">
-        <v>-44.48598759999999</v>
+        <v>-45.60815979999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1553629154159673</v>
+        <v>0.1580351816456251</v>
       </c>
       <c r="T60">
-        <v>2.135585150804427</v>
+        <v>2.187672593506973</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2627293620416694</v>
+        <v>0.2582763220070649</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2039164244747063</v>
+        <v>0.2058164244747063</v>
       </c>
       <c r="C61">
-        <v>-111.9731823227241</v>
+        <v>-118.2770540719732</v>
       </c>
       <c r="D61">
-        <v>130.1078176772758</v>
+        <v>128.5629459280267</v>
       </c>
       <c r="E61">
-        <v>248.7809999999999</v>
+        <v>253.54</v>
       </c>
       <c r="F61">
-        <v>280.7809999999999</v>
+        <v>285.54</v>
       </c>
       <c r="G61">
         <v>38.7</v>
@@ -6283,28 +6283,28 @@
         <v>17.1</v>
       </c>
       <c r="M61">
-        <v>66.20815979999999</v>
+        <v>67.330332</v>
       </c>
       <c r="N61">
-        <v>-49.10815979999999</v>
+        <v>-50.230332</v>
       </c>
       <c r="O61">
         <v>-0</v>
       </c>
       <c r="P61">
-        <v>-49.10815979999999</v>
+        <v>-50.230332</v>
       </c>
       <c r="Q61">
-        <v>-45.60815979999999</v>
+        <v>-46.730332</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1580351816456251</v>
+        <v>0.1608410611867657</v>
       </c>
       <c r="T61">
-        <v>2.187672593506973</v>
+        <v>2.242364408344648</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2582763220070649</v>
+        <v>0.2539717166402804</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2058164244747063</v>
+        <v>0.2077164244747063</v>
       </c>
       <c r="C62">
-        <v>-118.2770540719732</v>
+        <v>-124.5446693841982</v>
       </c>
       <c r="D62">
-        <v>128.5629459280267</v>
+        <v>127.0543306158018</v>
       </c>
       <c r="E62">
-        <v>253.54</v>
+        <v>258.299</v>
       </c>
       <c r="F62">
-        <v>285.54</v>
+        <v>290.299</v>
       </c>
       <c r="G62">
         <v>38.7</v>
@@ -6365,28 +6365,28 @@
         <v>17.1</v>
       </c>
       <c r="M62">
-        <v>67.330332</v>
+        <v>68.45250419999999</v>
       </c>
       <c r="N62">
-        <v>-50.230332</v>
+        <v>-51.35250419999999</v>
       </c>
       <c r="O62">
         <v>-0</v>
       </c>
       <c r="P62">
-        <v>-50.230332</v>
+        <v>-51.35250419999999</v>
       </c>
       <c r="Q62">
-        <v>-46.730332</v>
+        <v>-47.85250419999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1608410611867657</v>
+        <v>0.1637908319864264</v>
       </c>
       <c r="T62">
-        <v>2.242364408344648</v>
+        <v>2.299860931635537</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2539717166402804</v>
+        <v>0.2498082458756856</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2077164244747063</v>
+        <v>0.2096164244747063</v>
       </c>
       <c r="C63">
-        <v>-124.5446693841982</v>
+        <v>-130.7772898037874</v>
       </c>
       <c r="D63">
-        <v>127.0543306158018</v>
+        <v>125.5807101962126</v>
       </c>
       <c r="E63">
-        <v>258.299</v>
+        <v>263.058</v>
       </c>
       <c r="F63">
-        <v>290.299</v>
+        <v>295.058</v>
       </c>
       <c r="G63">
         <v>38.7</v>
@@ -6447,28 +6447,28 @@
         <v>17.1</v>
       </c>
       <c r="M63">
-        <v>68.45250419999999</v>
+        <v>69.5746764</v>
       </c>
       <c r="N63">
-        <v>-51.35250419999999</v>
+        <v>-52.4746764</v>
       </c>
       <c r="O63">
         <v>-0</v>
       </c>
       <c r="P63">
-        <v>-51.35250419999999</v>
+        <v>-52.4746764</v>
       </c>
       <c r="Q63">
-        <v>-47.85250419999999</v>
+        <v>-48.9746764</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1637908319864264</v>
+        <v>0.166895853880806</v>
       </c>
       <c r="T63">
-        <v>2.299860931635537</v>
+        <v>2.360383587731209</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2498082458756856</v>
+        <v>0.2457790806196262</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2096164244747063</v>
+        <v>0.2115164244747063</v>
       </c>
       <c r="C64">
-        <v>-130.7772898037874</v>
+        <v>-136.9761190188404</v>
       </c>
       <c r="D64">
-        <v>125.5807101962126</v>
+        <v>124.1408809811596</v>
       </c>
       <c r="E64">
-        <v>263.058</v>
+        <v>267.817</v>
       </c>
       <c r="F64">
-        <v>295.058</v>
+        <v>299.817</v>
       </c>
       <c r="G64">
         <v>38.7</v>
@@ -6529,28 +6529,28 @@
         <v>17.1</v>
       </c>
       <c r="M64">
-        <v>69.5746764</v>
+        <v>70.69684860000001</v>
       </c>
       <c r="N64">
-        <v>-52.4746764</v>
+        <v>-53.59684860000001</v>
       </c>
       <c r="O64">
         <v>-0</v>
       </c>
       <c r="P64">
-        <v>-52.4746764</v>
+        <v>-53.59684860000001</v>
       </c>
       <c r="Q64">
-        <v>-48.9746764</v>
+        <v>-50.09684860000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.166895853880806</v>
+        <v>0.1701687147965035</v>
       </c>
       <c r="T64">
-        <v>2.360383587731209</v>
+        <v>2.424177738750971</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2457790806196262</v>
+        <v>0.2418778253716956</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2115164244747063</v>
+        <v>0.2134164244747063</v>
       </c>
       <c r="C65">
-        <v>-136.9761190188404</v>
+        <v>-143.1423061402898</v>
       </c>
       <c r="D65">
-        <v>124.1408809811596</v>
+        <v>122.7336938597102</v>
       </c>
       <c r="E65">
-        <v>267.817</v>
+        <v>272.576</v>
       </c>
       <c r="F65">
-        <v>299.817</v>
+        <v>304.576</v>
       </c>
       <c r="G65">
         <v>38.7</v>
@@ -6611,28 +6611,28 @@
         <v>17.1</v>
       </c>
       <c r="M65">
-        <v>70.69684860000001</v>
+        <v>71.81902079999999</v>
       </c>
       <c r="N65">
-        <v>-53.59684860000001</v>
+        <v>-54.71902079999999</v>
       </c>
       <c r="O65">
         <v>-0</v>
       </c>
       <c r="P65">
-        <v>-53.59684860000001</v>
+        <v>-54.71902079999999</v>
       </c>
       <c r="Q65">
-        <v>-50.09684860000001</v>
+        <v>-51.21902079999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1701687147965035</v>
+        <v>0.1736234013186286</v>
       </c>
       <c r="T65">
-        <v>2.424177738750971</v>
+        <v>2.491516009271831</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2418778253716956</v>
+        <v>0.2380984843502629</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2134164244747063</v>
+        <v>0.2153164244747063</v>
       </c>
       <c r="C66">
-        <v>-143.1423061402898</v>
+        <v>-149.2769487605024</v>
       </c>
       <c r="D66">
-        <v>122.7336938597102</v>
+        <v>121.3580512394976</v>
       </c>
       <c r="E66">
-        <v>272.576</v>
+        <v>277.335</v>
       </c>
       <c r="F66">
-        <v>304.576</v>
+        <v>309.335</v>
       </c>
       <c r="G66">
         <v>38.7</v>
@@ -6693,28 +6693,28 @@
         <v>17.1</v>
       </c>
       <c r="M66">
-        <v>71.81902079999999</v>
+        <v>72.941193</v>
       </c>
       <c r="N66">
-        <v>-54.71902079999999</v>
+        <v>-55.841193</v>
       </c>
       <c r="O66">
         <v>-0</v>
       </c>
       <c r="P66">
-        <v>-54.71902079999999</v>
+        <v>-55.841193</v>
       </c>
       <c r="Q66">
-        <v>-51.21902079999999</v>
+        <v>-52.341193</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1736234013186286</v>
+        <v>0.1772754984991609</v>
       </c>
       <c r="T66">
-        <v>2.491516009271831</v>
+        <v>2.562702180965313</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2380984843502629</v>
+        <v>0.2344354307448742</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2153164244747063</v>
+        <v>0.2172164244747063</v>
       </c>
       <c r="C67">
-        <v>-149.2769487605024</v>
+        <v>-155.3810958084684</v>
       </c>
       <c r="D67">
-        <v>121.3580512394976</v>
+        <v>120.0129041915316</v>
       </c>
       <c r="E67">
-        <v>277.335</v>
+        <v>282.094</v>
       </c>
       <c r="F67">
-        <v>309.335</v>
+        <v>314.094</v>
       </c>
       <c r="G67">
         <v>38.7</v>
@@ -6775,28 +6775,28 @@
         <v>17.1</v>
       </c>
       <c r="M67">
-        <v>72.941193</v>
+        <v>74.06336520000001</v>
       </c>
       <c r="N67">
-        <v>-55.841193</v>
+        <v>-56.96336520000001</v>
       </c>
       <c r="O67">
         <v>-0</v>
       </c>
       <c r="P67">
-        <v>-55.841193</v>
+        <v>-56.96336520000001</v>
       </c>
       <c r="Q67">
-        <v>-52.341193</v>
+        <v>-53.46336520000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1772754984991609</v>
+        <v>0.1811424249256067</v>
       </c>
       <c r="T67">
-        <v>2.562702180965313</v>
+        <v>2.638075774523116</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2344354307448742</v>
+        <v>0.2308833787638912</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2172164244747063</v>
+        <v>0.2191164244747063</v>
       </c>
       <c r="C68">
-        <v>-155.3810958084684</v>
+        <v>-161.4557502171895</v>
       </c>
       <c r="D68">
-        <v>120.0129041915316</v>
+        <v>118.6972497828105</v>
       </c>
       <c r="E68">
-        <v>282.094</v>
+        <v>286.853</v>
       </c>
       <c r="F68">
-        <v>314.094</v>
+        <v>318.853</v>
       </c>
       <c r="G68">
         <v>38.7</v>
@@ -6857,28 +6857,28 @@
         <v>17.1</v>
       </c>
       <c r="M68">
-        <v>74.06336520000001</v>
+        <v>75.1855374</v>
       </c>
       <c r="N68">
-        <v>-56.96336520000001</v>
+        <v>-58.0855374</v>
       </c>
       <c r="O68">
         <v>-0</v>
       </c>
       <c r="P68">
-        <v>-56.96336520000001</v>
+        <v>-58.0855374</v>
       </c>
       <c r="Q68">
-        <v>-53.46336520000001</v>
+        <v>-54.5855374</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1811424249256067</v>
+        <v>0.185243710529413</v>
       </c>
       <c r="T68">
-        <v>2.638075774523116</v>
+        <v>2.71801746466018</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2308833787638912</v>
+        <v>0.2274373581853257</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2191164244747063</v>
+        <v>0.2210164244747063</v>
       </c>
       <c r="C69">
-        <v>-161.4557502171895</v>
+        <v>-167.5018714175191</v>
       </c>
       <c r="D69">
-        <v>118.6972497828105</v>
+        <v>117.410128582481</v>
       </c>
       <c r="E69">
-        <v>286.853</v>
+        <v>291.612</v>
       </c>
       <c r="F69">
-        <v>318.853</v>
+        <v>323.612</v>
       </c>
       <c r="G69">
         <v>38.7</v>
@@ -6939,28 +6939,28 @@
         <v>17.1</v>
       </c>
       <c r="M69">
-        <v>75.1855374</v>
+        <v>76.30770960000001</v>
       </c>
       <c r="N69">
-        <v>-58.0855374</v>
+        <v>-59.20770960000001</v>
       </c>
       <c r="O69">
         <v>-0</v>
       </c>
       <c r="P69">
-        <v>-58.0855374</v>
+        <v>-59.20770960000001</v>
       </c>
       <c r="Q69">
-        <v>-54.5855374</v>
+        <v>-55.70770960000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.185243710529413</v>
+        <v>0.1896013264834571</v>
       </c>
       <c r="T69">
-        <v>2.71801746466018</v>
+        <v>2.80295551043081</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2274373581853257</v>
+        <v>0.2240926911531885</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2210164244747063</v>
+        <v>0.2229164244747063</v>
       </c>
       <c r="C70">
-        <v>-167.5018714175191</v>
+        <v>-173.5203776714891</v>
       </c>
       <c r="D70">
-        <v>117.410128582481</v>
+        <v>116.1506223285109</v>
       </c>
       <c r="E70">
-        <v>291.612</v>
+        <v>296.371</v>
       </c>
       <c r="F70">
-        <v>323.612</v>
+        <v>328.371</v>
       </c>
       <c r="G70">
         <v>38.7</v>
@@ -7021,28 +7021,28 @@
         <v>17.1</v>
       </c>
       <c r="M70">
-        <v>76.30770960000001</v>
+        <v>77.42988180000002</v>
       </c>
       <c r="N70">
-        <v>-59.20770960000001</v>
+        <v>-60.32988180000002</v>
       </c>
       <c r="O70">
         <v>-0</v>
       </c>
       <c r="P70">
-        <v>-59.20770960000001</v>
+        <v>-60.32988180000002</v>
       </c>
       <c r="Q70">
-        <v>-55.70770960000001</v>
+        <v>-56.82988180000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1896013264834571</v>
+        <v>0.1942400789506655</v>
       </c>
       <c r="T70">
-        <v>2.80295551043081</v>
+        <v>2.893373430122127</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2240926911531885</v>
+        <v>0.2208449709915481</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2229164244747063</v>
+        <v>0.2248164244747063</v>
       </c>
       <c r="C71">
-        <v>-173.5203776714891</v>
+        <v>-179.512148257047</v>
       </c>
       <c r="D71">
-        <v>116.1506223285109</v>
+        <v>114.917851742953</v>
       </c>
       <c r="E71">
-        <v>296.371</v>
+        <v>301.13</v>
       </c>
       <c r="F71">
-        <v>328.371</v>
+        <v>333.13</v>
       </c>
       <c r="G71">
         <v>38.7</v>
@@ -7103,28 +7103,28 @@
         <v>17.1</v>
       </c>
       <c r="M71">
-        <v>77.42988180000002</v>
+        <v>78.552054</v>
       </c>
       <c r="N71">
-        <v>-60.32988180000002</v>
+        <v>-61.452054</v>
       </c>
       <c r="O71">
         <v>-0</v>
       </c>
       <c r="P71">
-        <v>-60.32988180000002</v>
+        <v>-61.452054</v>
       </c>
       <c r="Q71">
-        <v>-56.82988180000002</v>
+        <v>-57.952054</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1942400789506655</v>
+        <v>0.1991880815823543</v>
       </c>
       <c r="T71">
-        <v>2.893373430122127</v>
+        <v>2.989819211126198</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2208449709915481</v>
+        <v>0.217690042834526</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2248164244747063</v>
+        <v>0.2267164244747063</v>
       </c>
       <c r="C72">
-        <v>-179.512148257047</v>
+        <v>-185.4780255151267</v>
       </c>
       <c r="D72">
-        <v>114.917851742953</v>
+        <v>113.7109744848733</v>
       </c>
       <c r="E72">
-        <v>301.13</v>
+        <v>305.889</v>
       </c>
       <c r="F72">
-        <v>333.13</v>
+        <v>337.889</v>
       </c>
       <c r="G72">
         <v>38.7</v>
@@ -7185,28 +7185,28 @@
         <v>17.1</v>
       </c>
       <c r="M72">
-        <v>78.552054</v>
+        <v>79.67422620000001</v>
       </c>
       <c r="N72">
-        <v>-61.452054</v>
+        <v>-62.57422620000001</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-61.452054</v>
+        <v>-62.57422620000001</v>
       </c>
       <c r="Q72">
-        <v>-57.952054</v>
+        <v>-59.07422620000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1991880815823543</v>
+        <v>0.2044773257748493</v>
       </c>
       <c r="T72">
-        <v>2.989819211126198</v>
+        <v>3.092916425302964</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.217690042834526</v>
+        <v>0.2146239858931946</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2267164244747063</v>
+        <v>0.2286164244747063</v>
       </c>
       <c r="C73">
-        <v>-185.4780255151267</v>
+        <v>-191.4188167690692</v>
       </c>
       <c r="D73">
-        <v>113.7109744848733</v>
+        <v>112.5291832309307</v>
       </c>
       <c r="E73">
-        <v>305.889</v>
+        <v>310.648</v>
       </c>
       <c r="F73">
-        <v>337.889</v>
+        <v>342.648</v>
       </c>
       <c r="G73">
         <v>38.7</v>
@@ -7267,28 +7267,28 @@
         <v>17.1</v>
       </c>
       <c r="M73">
-        <v>79.67422619999999</v>
+        <v>80.7963984</v>
       </c>
       <c r="N73">
-        <v>-62.57422619999999</v>
+        <v>-63.6963984</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-62.57422619999999</v>
+        <v>-63.6963984</v>
       </c>
       <c r="Q73">
-        <v>-59.07422619999999</v>
+        <v>-60.1963984</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2044773257748493</v>
+        <v>0.210144373123951</v>
       </c>
       <c r="T73">
-        <v>3.092916425302963</v>
+        <v>3.20337772620664</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2146239858931946</v>
+        <v>0.2116430972002337</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2286164244747063</v>
+        <v>0.2305164244747063</v>
       </c>
       <c r="C74">
-        <v>-191.4188167690692</v>
+        <v>-197.3352961255844</v>
       </c>
       <c r="D74">
-        <v>112.5291832309307</v>
+        <v>111.3717038744155</v>
       </c>
       <c r="E74">
-        <v>310.648</v>
+        <v>315.407</v>
       </c>
       <c r="F74">
-        <v>342.648</v>
+        <v>347.407</v>
       </c>
       <c r="G74">
         <v>38.7</v>
@@ -7349,28 +7349,28 @@
         <v>17.1</v>
       </c>
       <c r="M74">
-        <v>80.7963984</v>
+        <v>81.9185706</v>
       </c>
       <c r="N74">
-        <v>-63.6963984</v>
+        <v>-64.81857059999999</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-63.6963984</v>
+        <v>-64.81857059999999</v>
       </c>
       <c r="Q74">
-        <v>-60.1963984</v>
+        <v>-61.31857059999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.210144373123951</v>
+        <v>0.2162312017581714</v>
       </c>
       <c r="T74">
-        <v>3.20337772620664</v>
+        <v>3.322021345695775</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2116430972002337</v>
+        <v>0.2087438766906415</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2305164244747063</v>
+        <v>0.2324164244747063</v>
       </c>
       <c r="C75">
-        <v>-197.3352961255844</v>
+        <v>-203.2282061656949</v>
       </c>
       <c r="D75">
-        <v>111.3717038744155</v>
+        <v>110.2377938343051</v>
       </c>
       <c r="E75">
-        <v>315.407</v>
+        <v>320.166</v>
       </c>
       <c r="F75">
-        <v>347.407</v>
+        <v>352.166</v>
       </c>
       <c r="G75">
         <v>38.7</v>
@@ -7431,28 +7431,28 @@
         <v>17.1</v>
       </c>
       <c r="M75">
-        <v>81.9185706</v>
+        <v>83.0407428</v>
       </c>
       <c r="N75">
-        <v>-64.81857059999999</v>
+        <v>-65.94074280000001</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-64.81857059999999</v>
+        <v>-65.94074280000001</v>
       </c>
       <c r="Q75">
-        <v>-61.31857059999999</v>
+        <v>-62.44074280000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2162312017581714</v>
+        <v>0.2227862479796395</v>
       </c>
       <c r="T75">
-        <v>3.322021345695775</v>
+        <v>3.449791397453304</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2087438766906415</v>
+        <v>0.2059230134921192</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2324164244747063</v>
+        <v>0.2343164244747063</v>
       </c>
       <c r="C76">
-        <v>-203.2282061656949</v>
+        <v>-209.0982595334256</v>
       </c>
       <c r="D76">
-        <v>110.2377938343051</v>
+        <v>109.1267404665743</v>
       </c>
       <c r="E76">
-        <v>320.166</v>
+        <v>324.925</v>
       </c>
       <c r="F76">
-        <v>352.166</v>
+        <v>356.925</v>
       </c>
       <c r="G76">
         <v>38.7</v>
@@ -7513,28 +7513,28 @@
         <v>17.1</v>
       </c>
       <c r="M76">
-        <v>83.0407428</v>
+        <v>84.162915</v>
       </c>
       <c r="N76">
-        <v>-65.94074280000001</v>
+        <v>-67.062915</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-65.94074280000001</v>
+        <v>-67.062915</v>
       </c>
       <c r="Q76">
-        <v>-62.44074280000001</v>
+        <v>-63.562915</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2227862479796395</v>
+        <v>0.2298656978988251</v>
       </c>
       <c r="T76">
-        <v>3.449791397453304</v>
+        <v>3.587783053351437</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2059230134921192</v>
+        <v>0.2031773733122242</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2343164244747063</v>
+        <v>0.2362164244747063</v>
       </c>
       <c r="C77">
-        <v>-209.0982595334256</v>
+        <v>-214.9461404293803</v>
       </c>
       <c r="D77">
-        <v>109.1267404665743</v>
+        <v>108.0378595706197</v>
       </c>
       <c r="E77">
-        <v>324.925</v>
+        <v>329.684</v>
       </c>
       <c r="F77">
-        <v>356.925</v>
+        <v>361.684</v>
       </c>
       <c r="G77">
         <v>38.7</v>
@@ -7595,28 +7595,28 @@
         <v>17.1</v>
       </c>
       <c r="M77">
-        <v>84.162915</v>
+        <v>85.28508719999999</v>
       </c>
       <c r="N77">
-        <v>-67.062915</v>
+        <v>-68.1850872</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-67.062915</v>
+        <v>-68.1850872</v>
       </c>
       <c r="Q77">
-        <v>-63.562915</v>
+        <v>-64.6850872</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2298656978988251</v>
+        <v>0.2375351019779429</v>
       </c>
       <c r="T77">
-        <v>3.587783053351437</v>
+        <v>3.737274013907747</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2031773733122242</v>
+        <v>0.2005039868212739</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2362164244747063</v>
+        <v>0.2381164244747063</v>
       </c>
       <c r="C78">
-        <v>-214.9461404293803</v>
+        <v>-220.7725060157822</v>
       </c>
       <c r="D78">
-        <v>108.0378595706197</v>
+        <v>106.9704939842178</v>
       </c>
       <c r="E78">
-        <v>329.684</v>
+        <v>334.443</v>
       </c>
       <c r="F78">
-        <v>361.684</v>
+        <v>366.443</v>
       </c>
       <c r="G78">
         <v>38.7</v>
@@ -7677,28 +7677,28 @@
         <v>17.1</v>
       </c>
       <c r="M78">
-        <v>85.28508719999999</v>
+        <v>86.4072594</v>
       </c>
       <c r="N78">
-        <v>-68.1850872</v>
+        <v>-69.30725939999999</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-68.1850872</v>
+        <v>-69.30725939999999</v>
       </c>
       <c r="Q78">
-        <v>-64.6850872</v>
+        <v>-65.80725939999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2375351019779429</v>
+        <v>0.2458714107595925</v>
       </c>
       <c r="T78">
-        <v>3.737274013907747</v>
+        <v>3.899764188425475</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2005039868212739</v>
+        <v>0.1979000389404783</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2381164244747063</v>
+        <v>0.2400164244747063</v>
       </c>
       <c r="C79">
-        <v>-220.7725060157822</v>
+        <v>-226.5779877390439</v>
       </c>
       <c r="D79">
-        <v>106.9704939842178</v>
+        <v>105.9240122609561</v>
       </c>
       <c r="E79">
-        <v>334.443</v>
+        <v>339.202</v>
       </c>
       <c r="F79">
-        <v>366.443</v>
+        <v>371.202</v>
       </c>
       <c r="G79">
         <v>38.7</v>
@@ -7759,28 +7759,28 @@
         <v>17.1</v>
       </c>
       <c r="M79">
-        <v>86.4072594</v>
+        <v>87.52943160000001</v>
       </c>
       <c r="N79">
-        <v>-69.30725939999999</v>
+        <v>-70.42943160000002</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-69.30725939999999</v>
+        <v>-70.42943160000002</v>
       </c>
       <c r="Q79">
-        <v>-65.80725939999999</v>
+        <v>-66.92943160000002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2458714107595925</v>
+        <v>0.2549655657941194</v>
       </c>
       <c r="T79">
-        <v>3.899764188425475</v>
+        <v>4.077026196990269</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1979000389404783</v>
+        <v>0.1953628589540617</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2400164244747063</v>
+        <v>0.2419164244747063</v>
       </c>
       <c r="C80">
-        <v>-226.5779877390439</v>
+        <v>-232.3631925754562</v>
       </c>
       <c r="D80">
-        <v>105.9240122609561</v>
+        <v>104.8978074245438</v>
       </c>
       <c r="E80">
-        <v>339.202</v>
+        <v>343.961</v>
       </c>
       <c r="F80">
-        <v>371.202</v>
+        <v>375.961</v>
       </c>
       <c r="G80">
         <v>38.7</v>
@@ -7841,28 +7841,28 @@
         <v>17.1</v>
       </c>
       <c r="M80">
-        <v>87.52943160000001</v>
+        <v>88.6516038</v>
       </c>
       <c r="N80">
-        <v>-70.42943160000002</v>
+        <v>-71.55160380000001</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-70.42943160000002</v>
+        <v>-71.55160380000001</v>
       </c>
       <c r="Q80">
-        <v>-66.92943160000002</v>
+        <v>-68.05160380000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2549655657941194</v>
+        <v>0.2649258308319347</v>
       </c>
       <c r="T80">
-        <v>4.077026196990269</v>
+        <v>4.271170301608854</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1953628589540617</v>
+        <v>0.1928899113723648</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2419164244747063</v>
+        <v>0.2438164244747063</v>
       </c>
       <c r="C81">
-        <v>-232.3631925754562</v>
+        <v>-238.1287042051624</v>
       </c>
       <c r="D81">
-        <v>104.8978074245438</v>
+        <v>103.8912957948376</v>
       </c>
       <c r="E81">
-        <v>343.961</v>
+        <v>348.72</v>
       </c>
       <c r="F81">
-        <v>375.961</v>
+        <v>380.72</v>
       </c>
       <c r="G81">
         <v>38.7</v>
@@ -7923,28 +7923,28 @@
         <v>17.1</v>
       </c>
       <c r="M81">
-        <v>88.6516038</v>
+        <v>89.77377600000001</v>
       </c>
       <c r="N81">
-        <v>-71.55160380000001</v>
+        <v>-72.673776</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-71.55160380000001</v>
+        <v>-72.673776</v>
       </c>
       <c r="Q81">
-        <v>-68.05160380000001</v>
+        <v>-69.173776</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2649258308319347</v>
+        <v>0.2758821223735314</v>
       </c>
       <c r="T81">
-        <v>4.271170301608854</v>
+        <v>4.484728816689297</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1928899113723648</v>
+        <v>0.1904787874802103</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2438164244747063</v>
+        <v>0.2457164244747063</v>
       </c>
       <c r="C82">
-        <v>-238.1287042051624</v>
+        <v>-243.8750841191882</v>
       </c>
       <c r="D82">
-        <v>103.8912957948376</v>
+        <v>102.9039158808118</v>
       </c>
       <c r="E82">
-        <v>348.72</v>
+        <v>353.479</v>
       </c>
       <c r="F82">
-        <v>380.72</v>
+        <v>385.479</v>
       </c>
       <c r="G82">
         <v>38.7</v>
@@ -8005,28 +8005,28 @@
         <v>17.1</v>
       </c>
       <c r="M82">
-        <v>89.77377600000001</v>
+        <v>90.89594820000001</v>
       </c>
       <c r="N82">
-        <v>-72.673776</v>
+        <v>-73.7959482</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-72.673776</v>
+        <v>-73.7959482</v>
       </c>
       <c r="Q82">
-        <v>-69.173776</v>
+        <v>-70.2959482</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2758821223735314</v>
+        <v>0.2879917077616121</v>
       </c>
       <c r="T82">
-        <v>4.484728816689297</v>
+        <v>4.720767175462418</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1904787874802103</v>
+        <v>0.1881271975113189</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2457164244747063</v>
+        <v>0.2476164244747063</v>
       </c>
       <c r="C83">
-        <v>-243.8750841191882</v>
+        <v>-249.6028726639385</v>
       </c>
       <c r="D83">
-        <v>102.9039158808118</v>
+        <v>101.9351273360616</v>
       </c>
       <c r="E83">
-        <v>353.479</v>
+        <v>358.238</v>
       </c>
       <c r="F83">
-        <v>385.479</v>
+        <v>390.238</v>
       </c>
       <c r="G83">
         <v>38.7</v>
@@ -8087,28 +8087,28 @@
         <v>17.1</v>
       </c>
       <c r="M83">
-        <v>90.89594820000001</v>
+        <v>92.0181204</v>
       </c>
       <c r="N83">
-        <v>-73.7959482</v>
+        <v>-74.91812039999999</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-73.7959482</v>
+        <v>-74.91812039999999</v>
       </c>
       <c r="Q83">
-        <v>-70.2959482</v>
+        <v>-71.41812039999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2879917077616121</v>
+        <v>0.3014468026372572</v>
       </c>
       <c r="T83">
-        <v>4.720767175462418</v>
+        <v>4.983032018543664</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1881271975113189</v>
+        <v>0.1858329633953272</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2476164244747063</v>
+        <v>0.2495164244747063</v>
       </c>
       <c r="C84">
-        <v>-249.6028726639385</v>
+        <v>-255.3125900272435</v>
       </c>
       <c r="D84">
-        <v>101.9351273360616</v>
+        <v>100.9844099727565</v>
       </c>
       <c r="E84">
-        <v>358.238</v>
+        <v>362.997</v>
       </c>
       <c r="F84">
-        <v>390.238</v>
+        <v>394.997</v>
       </c>
       <c r="G84">
         <v>38.7</v>
@@ -8169,28 +8169,28 @@
         <v>17.1</v>
       </c>
       <c r="M84">
-        <v>92.0181204</v>
+        <v>93.14029260000001</v>
       </c>
       <c r="N84">
-        <v>-74.91812039999999</v>
+        <v>-76.04029260000001</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-74.91812039999999</v>
+        <v>-76.04029260000001</v>
       </c>
       <c r="Q84">
-        <v>-71.41812039999999</v>
+        <v>-72.54029260000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3014468026372572</v>
+        <v>0.3164848498512136</v>
       </c>
       <c r="T84">
-        <v>4.983032018543664</v>
+        <v>5.276151549046233</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1858329633953272</v>
+        <v>0.1835940120291183</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2495164244747063</v>
+        <v>0.2514164244747063</v>
       </c>
       <c r="C85">
-        <v>-255.3125900272435</v>
+        <v>-261.0047371697367</v>
       </c>
       <c r="D85">
-        <v>100.9844099727565</v>
+        <v>100.0512628302634</v>
       </c>
       <c r="E85">
-        <v>362.997</v>
+        <v>367.756</v>
       </c>
       <c r="F85">
-        <v>394.997</v>
+        <v>399.756</v>
       </c>
       <c r="G85">
         <v>38.7</v>
@@ -8251,28 +8251,28 @@
         <v>17.1</v>
       </c>
       <c r="M85">
-        <v>93.14029260000001</v>
+        <v>94.2624648</v>
       </c>
       <c r="N85">
-        <v>-76.04029260000001</v>
+        <v>-77.16246480000001</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-76.04029260000001</v>
+        <v>-77.16246480000001</v>
       </c>
       <c r="Q85">
-        <v>-72.54029260000001</v>
+        <v>-73.66246480000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3164848498512136</v>
+        <v>0.3334026529669144</v>
       </c>
       <c r="T85">
-        <v>5.276151549046233</v>
+        <v>5.605911020861623</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1835940120291183</v>
+        <v>0.1814083690287716</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2514164244747063</v>
+        <v>0.2533164244747063</v>
       </c>
       <c r="C86">
-        <v>-261.0047371697366</v>
+        <v>-266.6797967050659</v>
       </c>
       <c r="D86">
-        <v>100.0512628302634</v>
+        <v>99.13520329493409</v>
       </c>
       <c r="E86">
-        <v>367.756</v>
+        <v>372.515</v>
       </c>
       <c r="F86">
-        <v>399.756</v>
+        <v>404.515</v>
       </c>
       <c r="G86">
         <v>38.7</v>
@@ -8333,28 +8333,28 @@
         <v>17.1</v>
       </c>
       <c r="M86">
-        <v>94.2624648</v>
+        <v>95.384637</v>
       </c>
       <c r="N86">
-        <v>-77.16246480000001</v>
+        <v>-78.284637</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-77.16246480000001</v>
+        <v>-78.284637</v>
       </c>
       <c r="Q86">
-        <v>-73.66246480000001</v>
+        <v>-74.784637</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3334026529669142</v>
+        <v>0.3525761631647085</v>
       </c>
       <c r="T86">
-        <v>5.60591102086162</v>
+        <v>5.979638422252394</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1814083690287716</v>
+        <v>0.1792741529225508</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2533164244747063</v>
+        <v>0.2552164244747063</v>
       </c>
       <c r="C87">
-        <v>-266.6797967050659</v>
+        <v>-272.3382337321895</v>
       </c>
       <c r="D87">
-        <v>99.13520329493409</v>
+        <v>98.23576626781052</v>
       </c>
       <c r="E87">
-        <v>372.515</v>
+        <v>377.274</v>
       </c>
       <c r="F87">
-        <v>404.515</v>
+        <v>409.274</v>
       </c>
       <c r="G87">
         <v>38.7</v>
@@ -8415,28 +8415,28 @@
         <v>17.1</v>
       </c>
       <c r="M87">
-        <v>95.384637</v>
+        <v>96.50680920000001</v>
       </c>
       <c r="N87">
-        <v>-78.284637</v>
+        <v>-79.4068092</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-78.284637</v>
+        <v>-79.4068092</v>
       </c>
       <c r="Q87">
-        <v>-74.784637</v>
+        <v>-75.9068092</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3525761631647085</v>
+        <v>0.374488746247902</v>
       </c>
       <c r="T87">
-        <v>5.979638422252394</v>
+        <v>6.40675545241328</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1792741529225508</v>
+        <v>0.1771895697490329</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2552164244747063</v>
+        <v>0.2571164244747063</v>
       </c>
       <c r="C88">
-        <v>-272.3382337321895</v>
+        <v>-277.9804966227708</v>
       </c>
       <c r="D88">
-        <v>98.23576626781052</v>
+        <v>97.35250337722917</v>
       </c>
       <c r="E88">
-        <v>377.274</v>
+        <v>382.033</v>
       </c>
       <c r="F88">
-        <v>409.274</v>
+        <v>414.033</v>
       </c>
       <c r="G88">
         <v>38.7</v>
@@ -8497,28 +8497,28 @@
         <v>17.1</v>
       </c>
       <c r="M88">
-        <v>96.50680920000001</v>
+        <v>97.6289814</v>
       </c>
       <c r="N88">
-        <v>-79.4068092</v>
+        <v>-80.52898139999999</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-79.4068092</v>
+        <v>-80.52898139999999</v>
       </c>
       <c r="Q88">
-        <v>-75.9068092</v>
+        <v>-77.02898139999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.374488746247902</v>
+        <v>0.3997724959592791</v>
       </c>
       <c r="T88">
-        <v>6.40675545241328</v>
+        <v>6.899582794906609</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1771895697490329</v>
+        <v>0.1751529080277796</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2571164244747063</v>
+        <v>0.2590164244747063</v>
       </c>
       <c r="C89">
-        <v>-277.9804966227708</v>
+        <v>-283.6070177664746</v>
       </c>
       <c r="D89">
-        <v>97.35250337722917</v>
+        <v>96.48498223352536</v>
       </c>
       <c r="E89">
-        <v>382.033</v>
+        <v>386.792</v>
       </c>
       <c r="F89">
-        <v>414.033</v>
+        <v>418.792</v>
       </c>
       <c r="G89">
         <v>38.7</v>
@@ -8579,28 +8579,28 @@
         <v>17.1</v>
       </c>
       <c r="M89">
-        <v>97.6289814</v>
+        <v>98.75115359999999</v>
       </c>
       <c r="N89">
-        <v>-80.52898139999999</v>
+        <v>-81.65115359999999</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-80.52898139999999</v>
+        <v>-81.65115359999999</v>
       </c>
       <c r="Q89">
-        <v>-77.02898139999999</v>
+        <v>-78.15115359999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3997724959592791</v>
+        <v>0.4292702039558857</v>
       </c>
       <c r="T89">
-        <v>6.899582794906609</v>
+        <v>7.474548027815494</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1751529080277796</v>
+        <v>0.1731625340729185</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2590164244747063</v>
+        <v>0.2609164244747063</v>
       </c>
       <c r="C90">
-        <v>-283.6070177664746</v>
+        <v>-289.218214276766</v>
       </c>
       <c r="D90">
-        <v>96.48498223352536</v>
+        <v>95.63278572323397</v>
       </c>
       <c r="E90">
-        <v>386.792</v>
+        <v>391.551</v>
       </c>
       <c r="F90">
-        <v>418.792</v>
+        <v>423.551</v>
       </c>
       <c r="G90">
         <v>38.7</v>
@@ -8661,28 +8661,28 @@
         <v>17.1</v>
       </c>
       <c r="M90">
-        <v>98.75115359999999</v>
+        <v>99.8733258</v>
       </c>
       <c r="N90">
-        <v>-81.65115359999999</v>
+        <v>-82.77332580000001</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-81.65115359999999</v>
+        <v>-82.77332580000001</v>
       </c>
       <c r="Q90">
-        <v>-78.15115359999999</v>
+        <v>-79.27332580000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4292702039558857</v>
+        <v>0.4641311315882389</v>
       </c>
       <c r="T90">
-        <v>7.474548027815494</v>
+        <v>8.154052393980539</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1731625340729185</v>
+        <v>0.1712168876226609</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2609164244747063</v>
+        <v>0.2628164244747063</v>
       </c>
       <c r="C91">
-        <v>-289.218214276766</v>
+        <v>-294.8144886596334</v>
       </c>
       <c r="D91">
-        <v>95.63278572323397</v>
+        <v>94.79551134036662</v>
       </c>
       <c r="E91">
-        <v>391.551</v>
+        <v>396.31</v>
       </c>
       <c r="F91">
-        <v>423.551</v>
+        <v>428.31</v>
       </c>
       <c r="G91">
         <v>38.7</v>
@@ -8743,28 +8743,28 @@
         <v>17.1</v>
       </c>
       <c r="M91">
-        <v>99.8733258</v>
+        <v>100.995498</v>
       </c>
       <c r="N91">
-        <v>-82.77332580000001</v>
+        <v>-83.895498</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-82.77332580000001</v>
+        <v>-83.895498</v>
       </c>
       <c r="Q91">
-        <v>-79.27332580000001</v>
+        <v>-80.395498</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4641311315882389</v>
+        <v>0.5059642447470629</v>
       </c>
       <c r="T91">
-        <v>8.154052393980539</v>
+        <v>8.969457633378594</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1712168876226609</v>
+        <v>0.1693144777601868</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2628164244747063</v>
+        <v>0.2647164244747063</v>
       </c>
       <c r="C92">
-        <v>-294.8144886596334</v>
+        <v>-300.3962294474883</v>
       </c>
       <c r="D92">
-        <v>94.79551134036662</v>
+        <v>93.97277055251173</v>
       </c>
       <c r="E92">
-        <v>396.31</v>
+        <v>401.069</v>
       </c>
       <c r="F92">
-        <v>428.31</v>
+        <v>433.069</v>
       </c>
       <c r="G92">
         <v>38.7</v>
@@ -8825,28 +8825,28 @@
         <v>17.1</v>
       </c>
       <c r="M92">
-        <v>100.995498</v>
+        <v>102.1176702</v>
       </c>
       <c r="N92">
-        <v>-83.895498</v>
+        <v>-85.0176702</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-83.895498</v>
+        <v>-85.0176702</v>
       </c>
       <c r="Q92">
-        <v>-80.395498</v>
+        <v>-81.5176702</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5059642447470629</v>
+        <v>0.5570936052745143</v>
       </c>
       <c r="T92">
-        <v>8.969457633378594</v>
+        <v>9.966064037087328</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1693144777601868</v>
+        <v>0.1674538791034816</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2647164244747063</v>
+        <v>0.2666164244747063</v>
       </c>
       <c r="C93">
-        <v>-300.3962294474883</v>
+        <v>-305.9638118003386</v>
       </c>
       <c r="D93">
-        <v>93.97277055251173</v>
+        <v>93.16418819966133</v>
       </c>
       <c r="E93">
-        <v>401.069</v>
+        <v>405.828</v>
       </c>
       <c r="F93">
-        <v>433.069</v>
+        <v>437.828</v>
       </c>
       <c r="G93">
         <v>38.7</v>
@@ -8907,28 +8907,28 @@
         <v>17.1</v>
       </c>
       <c r="M93">
-        <v>102.1176702</v>
+        <v>103.2398424</v>
       </c>
       <c r="N93">
-        <v>-85.0176702</v>
+        <v>-86.13984239999999</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-85.0176702</v>
+        <v>-86.13984239999999</v>
       </c>
       <c r="Q93">
-        <v>-81.5176702</v>
+        <v>-82.63984239999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5570936052745143</v>
+        <v>0.6210053059338287</v>
       </c>
       <c r="T93">
-        <v>9.966064037087328</v>
+        <v>11.21182204172325</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1674538791034816</v>
+        <v>0.1656337282436612</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2666164244747063</v>
+        <v>0.2685164244747063</v>
       </c>
       <c r="C94">
-        <v>-305.9638118003386</v>
+        <v>-311.5175980761908</v>
       </c>
       <c r="D94">
-        <v>93.16418819966133</v>
+        <v>92.36940192380918</v>
       </c>
       <c r="E94">
-        <v>405.828</v>
+        <v>410.587</v>
       </c>
       <c r="F94">
-        <v>437.828</v>
+        <v>442.587</v>
       </c>
       <c r="G94">
         <v>38.7</v>
@@ -8989,28 +8989,28 @@
         <v>17.1</v>
       </c>
       <c r="M94">
-        <v>103.2398424</v>
+        <v>104.3620146</v>
       </c>
       <c r="N94">
-        <v>-86.13984239999999</v>
+        <v>-87.26201459999999</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-86.13984239999999</v>
+        <v>-87.26201459999999</v>
       </c>
       <c r="Q94">
-        <v>-82.63984239999999</v>
+        <v>-83.76201459999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6210053059338287</v>
+        <v>0.7031774924958044</v>
       </c>
       <c r="T94">
-        <v>11.21182204172325</v>
+        <v>12.81351090482657</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1656337282436612</v>
+        <v>0.1638527204130842</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2685164244747063</v>
+        <v>0.2704164244747063</v>
       </c>
       <c r="C95">
-        <v>-311.5175980761908</v>
+        <v>-317.0579383725012</v>
       </c>
       <c r="D95">
-        <v>92.36940192380918</v>
+        <v>91.58806162749885</v>
       </c>
       <c r="E95">
-        <v>410.587</v>
+        <v>415.346</v>
       </c>
       <c r="F95">
-        <v>442.587</v>
+        <v>447.346</v>
       </c>
       <c r="G95">
         <v>38.7</v>
@@ -9071,28 +9071,28 @@
         <v>17.1</v>
       </c>
       <c r="M95">
-        <v>104.3620146</v>
+        <v>105.4841868</v>
       </c>
       <c r="N95">
-        <v>-87.26201459999999</v>
+        <v>-88.38418680000001</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-87.26201459999999</v>
+        <v>-88.38418680000001</v>
       </c>
       <c r="Q95">
-        <v>-83.76201459999999</v>
+        <v>-84.88418680000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7031774924958044</v>
+        <v>0.812740407911772</v>
       </c>
       <c r="T95">
-        <v>12.81351090482657</v>
+        <v>14.949096055631</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1638527204130842</v>
+        <v>0.1621096063661364</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2704164244747063</v>
+        <v>0.2723164244747063</v>
       </c>
       <c r="C96">
-        <v>-317.0579383725012</v>
+        <v>-322.5851710403786</v>
       </c>
       <c r="D96">
-        <v>91.58806162749885</v>
+        <v>90.81982895962147</v>
       </c>
       <c r="E96">
-        <v>415.346</v>
+        <v>420.105</v>
       </c>
       <c r="F96">
-        <v>447.346</v>
+        <v>452.105</v>
       </c>
       <c r="G96">
         <v>38.7</v>
@@ -9153,28 +9153,28 @@
         <v>17.1</v>
       </c>
       <c r="M96">
-        <v>105.4841868</v>
+        <v>106.606359</v>
       </c>
       <c r="N96">
-        <v>-88.38418680000001</v>
+        <v>-89.506359</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-88.38418680000001</v>
+        <v>-89.506359</v>
       </c>
       <c r="Q96">
-        <v>-84.88418680000001</v>
+        <v>-86.006359</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.812740407911772</v>
+        <v>0.9661284894941269</v>
       </c>
       <c r="T96">
-        <v>14.949096055631</v>
+        <v>17.93891526675721</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1621096063661364</v>
+        <v>0.1604031894570193</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2723164244747063</v>
+        <v>0.2742164244747063</v>
       </c>
       <c r="C97">
-        <v>-322.5851710403786</v>
+        <v>-328.0996231731231</v>
       </c>
       <c r="D97">
-        <v>90.81982895962147</v>
+        <v>90.06437682687699</v>
       </c>
       <c r="E97">
-        <v>420.105</v>
+        <v>424.864</v>
       </c>
       <c r="F97">
-        <v>452.105</v>
+        <v>456.864</v>
       </c>
       <c r="G97">
         <v>38.7</v>
@@ -9235,28 +9235,28 @@
         <v>17.1</v>
       </c>
       <c r="M97">
-        <v>106.606359</v>
+        <v>107.7285312</v>
       </c>
       <c r="N97">
-        <v>-89.506359</v>
+        <v>-90.6285312</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-89.506359</v>
+        <v>-90.6285312</v>
       </c>
       <c r="Q97">
-        <v>-86.006359</v>
+        <v>-87.1285312</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9661284894941269</v>
+        <v>1.196210611867659</v>
       </c>
       <c r="T97">
-        <v>17.93891526675721</v>
+        <v>22.42364408344652</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1604031894570193</v>
+        <v>0.1587323229001752</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2742164244747063</v>
+        <v>0.2761164244747063</v>
       </c>
       <c r="C98">
-        <v>-328.0996231731229</v>
+        <v>-333.6016110705834</v>
       </c>
       <c r="D98">
-        <v>90.06437682687699</v>
+        <v>89.32138892941657</v>
       </c>
       <c r="E98">
-        <v>424.864</v>
+        <v>429.623</v>
       </c>
       <c r="F98">
-        <v>456.864</v>
+        <v>461.623</v>
       </c>
       <c r="G98">
         <v>38.7</v>
@@ -9317,28 +9317,28 @@
         <v>17.1</v>
       </c>
       <c r="M98">
-        <v>107.7285312</v>
+        <v>108.8507034</v>
       </c>
       <c r="N98">
-        <v>-90.6285312</v>
+        <v>-91.75070339999999</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-90.6285312</v>
+        <v>-91.75070339999999</v>
       </c>
       <c r="Q98">
-        <v>-87.1285312</v>
+        <v>-88.25070339999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.196210611867656</v>
+        <v>1.579680815823542</v>
       </c>
       <c r="T98">
-        <v>22.42364408344646</v>
+        <v>29.89819211126195</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1587323229001751</v>
+        <v>0.1570959072001735</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2761164244747063</v>
+        <v>0.2780164244747063</v>
       </c>
       <c r="C99">
-        <v>-333.6016110705834</v>
+        <v>-339.0914406807188</v>
       </c>
       <c r="D99">
-        <v>89.32138892941657</v>
+        <v>88.59055931928113</v>
       </c>
       <c r="E99">
-        <v>429.623</v>
+        <v>434.3819999999999</v>
       </c>
       <c r="F99">
-        <v>461.623</v>
+        <v>466.3819999999999</v>
       </c>
       <c r="G99">
         <v>38.7</v>
@@ -9399,28 +9399,28 @@
         <v>17.1</v>
       </c>
       <c r="M99">
-        <v>108.8507034</v>
+        <v>109.9728756</v>
       </c>
       <c r="N99">
-        <v>-91.75070339999999</v>
+        <v>-92.87287559999999</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-91.75070339999999</v>
+        <v>-92.87287559999999</v>
       </c>
       <c r="Q99">
-        <v>-88.25070339999999</v>
+        <v>-89.37287559999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.579680815823542</v>
+        <v>2.346621223735312</v>
       </c>
       <c r="T99">
-        <v>29.89819211126195</v>
+        <v>44.84728816689292</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1570959072001735</v>
+        <v>0.1554928877389472</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2780164244747063</v>
+        <v>0.2799164244747063</v>
       </c>
       <c r="C100">
-        <v>-339.0914406807188</v>
+        <v>-344.5694080196585</v>
       </c>
       <c r="D100">
-        <v>88.59055931928113</v>
+        <v>87.87159198034152</v>
       </c>
       <c r="E100">
-        <v>434.3819999999999</v>
+        <v>439.141</v>
       </c>
       <c r="F100">
-        <v>466.3819999999999</v>
+        <v>471.141</v>
       </c>
       <c r="G100">
         <v>38.7</v>
@@ -9481,28 +9481,28 @@
         <v>17.1</v>
       </c>
       <c r="M100">
-        <v>109.9728756</v>
+        <v>111.0950478</v>
       </c>
       <c r="N100">
-        <v>-92.87287559999999</v>
+        <v>-93.99504779999998</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-92.87287559999999</v>
+        <v>-93.99504779999998</v>
       </c>
       <c r="Q100">
-        <v>-89.37287559999999</v>
+        <v>-90.49504779999998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.346621223735312</v>
+        <v>4.647442447470624</v>
       </c>
       <c r="T100">
-        <v>44.84728816689292</v>
+        <v>89.69457633378585</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1554928877389472</v>
+        <v>0.1539222525092609</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2799164244747063</v>
-      </c>
-      <c r="C101">
-        <v>-344.5694080196585</v>
-      </c>
-      <c r="D101">
-        <v>87.87159198034152</v>
-      </c>
-      <c r="E101">
-        <v>439.141</v>
-      </c>
-      <c r="F101">
-        <v>471.141</v>
-      </c>
-      <c r="G101">
-        <v>38.7</v>
-      </c>
-      <c r="H101">
-        <v>443.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>20.6</v>
-      </c>
-      <c r="K101">
-        <v>3.5</v>
-      </c>
-      <c r="L101">
-        <v>17.1</v>
-      </c>
-      <c r="M101">
-        <v>111.0950478</v>
-      </c>
-      <c r="N101">
-        <v>-93.99504779999998</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-93.99504779999998</v>
-      </c>
-      <c r="Q101">
-        <v>-90.49504779999998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.647442447470624</v>
-      </c>
-      <c r="T101">
-        <v>89.69457633378585</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2358</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1539222525092609</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
